--- a/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3185300</v>
+        <v>3176600</v>
       </c>
       <c r="E8" s="3">
-        <v>2314500</v>
+        <v>2308200</v>
       </c>
       <c r="F8" s="3">
-        <v>2705700</v>
+        <v>2698300</v>
       </c>
       <c r="G8" s="3">
-        <v>3663000</v>
+        <v>3653000</v>
       </c>
       <c r="H8" s="3">
-        <v>3281400</v>
+        <v>3272400</v>
       </c>
       <c r="I8" s="3">
-        <v>2772600</v>
+        <v>2765100</v>
       </c>
       <c r="J8" s="3">
-        <v>2610300</v>
+        <v>2603200</v>
       </c>
       <c r="K8" s="3">
         <v>3004200</v>
@@ -996,25 +996,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-112200</v>
+        <v>-111900</v>
       </c>
       <c r="E15" s="3">
-        <v>-124200</v>
+        <v>-123900</v>
       </c>
       <c r="F15" s="3">
-        <v>-127500</v>
+        <v>-127200</v>
       </c>
       <c r="G15" s="3">
-        <v>-120600</v>
+        <v>-120300</v>
       </c>
       <c r="H15" s="3">
-        <v>-62400</v>
+        <v>-62300</v>
       </c>
       <c r="I15" s="3">
-        <v>-63800</v>
+        <v>-63700</v>
       </c>
       <c r="J15" s="3">
-        <v>-64100</v>
+        <v>-63900</v>
       </c>
       <c r="K15" s="3">
         <v>-67100</v>
@@ -1053,25 +1053,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2148000</v>
+        <v>2142100</v>
       </c>
       <c r="E17" s="3">
-        <v>1069200</v>
+        <v>1066300</v>
       </c>
       <c r="F17" s="3">
-        <v>1832000</v>
+        <v>1827000</v>
       </c>
       <c r="G17" s="3">
-        <v>2725200</v>
+        <v>2717800</v>
       </c>
       <c r="H17" s="3">
-        <v>1768800</v>
+        <v>1763900</v>
       </c>
       <c r="I17" s="3">
-        <v>1479200</v>
+        <v>1475100</v>
       </c>
       <c r="J17" s="3">
-        <v>1631500</v>
+        <v>1627000</v>
       </c>
       <c r="K17" s="3">
         <v>1743200</v>
@@ -1095,25 +1095,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1037300</v>
+        <v>1034500</v>
       </c>
       <c r="E18" s="3">
-        <v>1245200</v>
+        <v>1241800</v>
       </c>
       <c r="F18" s="3">
-        <v>873700</v>
+        <v>871400</v>
       </c>
       <c r="G18" s="3">
-        <v>937800</v>
+        <v>935300</v>
       </c>
       <c r="H18" s="3">
-        <v>1512600</v>
+        <v>1508500</v>
       </c>
       <c r="I18" s="3">
-        <v>1293400</v>
+        <v>1289900</v>
       </c>
       <c r="J18" s="3">
-        <v>978900</v>
+        <v>976200</v>
       </c>
       <c r="K18" s="3">
         <v>1261000</v>
@@ -1155,25 +1155,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-403900</v>
+        <v>-402800</v>
       </c>
       <c r="E20" s="3">
-        <v>-458700</v>
+        <v>-457400</v>
       </c>
       <c r="F20" s="3">
-        <v>-411500</v>
+        <v>-410400</v>
       </c>
       <c r="G20" s="3">
-        <v>-527900</v>
+        <v>-526400</v>
       </c>
       <c r="H20" s="3">
-        <v>-479400</v>
+        <v>-478100</v>
       </c>
       <c r="I20" s="3">
-        <v>-323700</v>
+        <v>-322800</v>
       </c>
       <c r="J20" s="3">
-        <v>-390200</v>
+        <v>-389100</v>
       </c>
       <c r="K20" s="3">
         <v>-447600</v>
@@ -1197,25 +1197,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>745500</v>
+        <v>743500</v>
       </c>
       <c r="E21" s="3">
-        <v>910700</v>
+        <v>908300</v>
       </c>
       <c r="F21" s="3">
-        <v>589700</v>
+        <v>588200</v>
       </c>
       <c r="G21" s="3">
-        <v>530500</v>
+        <v>529100</v>
       </c>
       <c r="H21" s="3">
-        <v>1095600</v>
+        <v>1092600</v>
       </c>
       <c r="I21" s="3">
-        <v>1033600</v>
+        <v>1030800</v>
       </c>
       <c r="J21" s="3">
-        <v>656800</v>
+        <v>655000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1281,25 +1281,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>633400</v>
+        <v>631700</v>
       </c>
       <c r="E23" s="3">
-        <v>786600</v>
+        <v>784400</v>
       </c>
       <c r="F23" s="3">
-        <v>462300</v>
+        <v>461000</v>
       </c>
       <c r="G23" s="3">
-        <v>410000</v>
+        <v>408800</v>
       </c>
       <c r="H23" s="3">
-        <v>1033200</v>
+        <v>1030400</v>
       </c>
       <c r="I23" s="3">
-        <v>969800</v>
+        <v>967100</v>
       </c>
       <c r="J23" s="3">
-        <v>588600</v>
+        <v>587000</v>
       </c>
       <c r="K23" s="3">
         <v>813400</v>
@@ -1323,25 +1323,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>72200</v>
+        <v>72000</v>
       </c>
       <c r="E24" s="3">
-        <v>105500</v>
+        <v>105200</v>
       </c>
       <c r="F24" s="3">
         <v>-10100</v>
       </c>
       <c r="G24" s="3">
-        <v>-17700</v>
+        <v>-17600</v>
       </c>
       <c r="H24" s="3">
-        <v>193100</v>
+        <v>192500</v>
       </c>
       <c r="I24" s="3">
-        <v>153200</v>
+        <v>152800</v>
       </c>
       <c r="J24" s="3">
-        <v>136800</v>
+        <v>136400</v>
       </c>
       <c r="K24" s="3">
         <v>133600</v>
@@ -1407,25 +1407,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>561200</v>
+        <v>559700</v>
       </c>
       <c r="E26" s="3">
-        <v>681100</v>
+        <v>679200</v>
       </c>
       <c r="F26" s="3">
-        <v>472400</v>
+        <v>471100</v>
       </c>
       <c r="G26" s="3">
-        <v>427600</v>
+        <v>426500</v>
       </c>
       <c r="H26" s="3">
-        <v>840200</v>
+        <v>837900</v>
       </c>
       <c r="I26" s="3">
-        <v>816600</v>
+        <v>814300</v>
       </c>
       <c r="J26" s="3">
-        <v>451900</v>
+        <v>450600</v>
       </c>
       <c r="K26" s="3">
         <v>679800</v>
@@ -1449,25 +1449,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>468000</v>
+        <v>466700</v>
       </c>
       <c r="E27" s="3">
-        <v>571600</v>
+        <v>570000</v>
       </c>
       <c r="F27" s="3">
-        <v>361800</v>
+        <v>360800</v>
       </c>
       <c r="G27" s="3">
-        <v>330700</v>
+        <v>329800</v>
       </c>
       <c r="H27" s="3">
-        <v>743000</v>
+        <v>741000</v>
       </c>
       <c r="I27" s="3">
-        <v>589900</v>
+        <v>588300</v>
       </c>
       <c r="J27" s="3">
-        <v>374800</v>
+        <v>373800</v>
       </c>
       <c r="K27" s="3">
         <v>597400</v>
@@ -1548,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>531300</v>
+        <v>529900</v>
       </c>
       <c r="J29" s="3">
-        <v>39000</v>
+        <v>38900</v>
       </c>
       <c r="K29" s="3">
         <v>38500</v>
@@ -1659,25 +1659,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>403900</v>
+        <v>402800</v>
       </c>
       <c r="E32" s="3">
-        <v>458700</v>
+        <v>457400</v>
       </c>
       <c r="F32" s="3">
-        <v>411500</v>
+        <v>410400</v>
       </c>
       <c r="G32" s="3">
-        <v>527900</v>
+        <v>526400</v>
       </c>
       <c r="H32" s="3">
-        <v>479400</v>
+        <v>478100</v>
       </c>
       <c r="I32" s="3">
-        <v>323700</v>
+        <v>322800</v>
       </c>
       <c r="J32" s="3">
-        <v>390200</v>
+        <v>389100</v>
       </c>
       <c r="K32" s="3">
         <v>447600</v>
@@ -1701,25 +1701,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>468000</v>
+        <v>466700</v>
       </c>
       <c r="E33" s="3">
-        <v>571600</v>
+        <v>570000</v>
       </c>
       <c r="F33" s="3">
-        <v>361800</v>
+        <v>360800</v>
       </c>
       <c r="G33" s="3">
-        <v>330700</v>
+        <v>329800</v>
       </c>
       <c r="H33" s="3">
-        <v>743000</v>
+        <v>741000</v>
       </c>
       <c r="I33" s="3">
-        <v>1121300</v>
+        <v>1118200</v>
       </c>
       <c r="J33" s="3">
-        <v>413800</v>
+        <v>412700</v>
       </c>
       <c r="K33" s="3">
         <v>635900</v>
@@ -1785,25 +1785,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>468000</v>
+        <v>466700</v>
       </c>
       <c r="E35" s="3">
-        <v>571600</v>
+        <v>570000</v>
       </c>
       <c r="F35" s="3">
-        <v>361800</v>
+        <v>360800</v>
       </c>
       <c r="G35" s="3">
-        <v>330700</v>
+        <v>329800</v>
       </c>
       <c r="H35" s="3">
-        <v>743000</v>
+        <v>741000</v>
       </c>
       <c r="I35" s="3">
-        <v>1121300</v>
+        <v>1118200</v>
       </c>
       <c r="J35" s="3">
-        <v>413800</v>
+        <v>412700</v>
       </c>
       <c r="K35" s="3">
         <v>635900</v>
@@ -1910,25 +1910,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6996500</v>
+        <v>6977400</v>
       </c>
       <c r="E41" s="3">
-        <v>7061700</v>
+        <v>7042400</v>
       </c>
       <c r="F41" s="3">
-        <v>7227000</v>
+        <v>7207200</v>
       </c>
       <c r="G41" s="3">
-        <v>6605000</v>
+        <v>6587000</v>
       </c>
       <c r="H41" s="3">
-        <v>6166700</v>
+        <v>6149900</v>
       </c>
       <c r="I41" s="3">
-        <v>7777300</v>
+        <v>7756100</v>
       </c>
       <c r="J41" s="3">
-        <v>8413600</v>
+        <v>8390700</v>
       </c>
       <c r="K41" s="3">
         <v>8810000</v>
@@ -1952,25 +1952,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>28248100</v>
+        <v>28171000</v>
       </c>
       <c r="E42" s="3">
-        <v>30622700</v>
+        <v>30539100</v>
       </c>
       <c r="F42" s="3">
-        <v>29748000</v>
+        <v>29666800</v>
       </c>
       <c r="G42" s="3">
-        <v>31386200</v>
+        <v>31300500</v>
       </c>
       <c r="H42" s="3">
-        <v>29924900</v>
+        <v>29843200</v>
       </c>
       <c r="I42" s="3">
-        <v>11551300</v>
+        <v>11519800</v>
       </c>
       <c r="J42" s="3">
-        <v>9343400</v>
+        <v>9317900</v>
       </c>
       <c r="K42" s="3">
         <v>14808500</v>
@@ -2162,25 +2162,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1161500</v>
+        <v>1158400</v>
       </c>
       <c r="E47" s="3">
-        <v>1146900</v>
+        <v>1143800</v>
       </c>
       <c r="F47" s="3">
-        <v>1177000</v>
+        <v>1173800</v>
       </c>
       <c r="G47" s="3">
-        <v>1278100</v>
+        <v>1274600</v>
       </c>
       <c r="H47" s="3">
-        <v>1170200</v>
+        <v>1167100</v>
       </c>
       <c r="I47" s="3">
-        <v>1208700</v>
+        <v>1205400</v>
       </c>
       <c r="J47" s="3">
-        <v>770600</v>
+        <v>768400</v>
       </c>
       <c r="K47" s="3">
         <v>734200</v>
@@ -2204,25 +2204,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1727500</v>
+        <v>1722800</v>
       </c>
       <c r="E48" s="3">
-        <v>1774700</v>
+        <v>1769800</v>
       </c>
       <c r="F48" s="3">
-        <v>1803000</v>
+        <v>1798100</v>
       </c>
       <c r="G48" s="3">
-        <v>1836700</v>
+        <v>1831700</v>
       </c>
       <c r="H48" s="3">
-        <v>1687600</v>
+        <v>1683000</v>
       </c>
       <c r="I48" s="3">
-        <v>1634400</v>
+        <v>1630000</v>
       </c>
       <c r="J48" s="3">
-        <v>1537000</v>
+        <v>1532800</v>
       </c>
       <c r="K48" s="3">
         <v>1694000</v>
@@ -2246,25 +2246,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>239700</v>
+        <v>239100</v>
       </c>
       <c r="E49" s="3">
-        <v>241600</v>
+        <v>241000</v>
       </c>
       <c r="F49" s="3">
-        <v>245100</v>
+        <v>244400</v>
       </c>
       <c r="G49" s="3">
-        <v>246900</v>
+        <v>246200</v>
       </c>
       <c r="H49" s="3">
-        <v>248700</v>
+        <v>248000</v>
       </c>
       <c r="I49" s="3">
-        <v>251100</v>
+        <v>250400</v>
       </c>
       <c r="J49" s="3">
-        <v>338300</v>
+        <v>337400</v>
       </c>
       <c r="K49" s="3">
         <v>494700</v>
@@ -2372,25 +2372,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>240500</v>
+        <v>239800</v>
       </c>
       <c r="E52" s="3">
-        <v>528800</v>
+        <v>527300</v>
       </c>
       <c r="F52" s="3">
-        <v>3676400</v>
+        <v>3666300</v>
       </c>
       <c r="G52" s="3">
-        <v>205400</v>
+        <v>204800</v>
       </c>
       <c r="H52" s="3">
-        <v>149900</v>
+        <v>149400</v>
       </c>
       <c r="I52" s="3">
-        <v>136900</v>
+        <v>136500</v>
       </c>
       <c r="J52" s="3">
-        <v>743100</v>
+        <v>741100</v>
       </c>
       <c r="K52" s="3">
         <v>23100</v>
@@ -2456,25 +2456,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>113169000</v>
+        <v>112860000</v>
       </c>
       <c r="E54" s="3">
-        <v>116329000</v>
+        <v>116011000</v>
       </c>
       <c r="F54" s="3">
-        <v>113374000</v>
+        <v>113064000</v>
       </c>
       <c r="G54" s="3">
-        <v>110910000</v>
+        <v>110607000</v>
       </c>
       <c r="H54" s="3">
-        <v>107609000</v>
+        <v>107315000</v>
       </c>
       <c r="I54" s="3">
-        <v>103698000</v>
+        <v>103415000</v>
       </c>
       <c r="J54" s="3">
-        <v>98155900</v>
+        <v>97887900</v>
       </c>
       <c r="K54" s="3">
         <v>99545800</v>
@@ -2534,25 +2534,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>532600</v>
+        <v>531200</v>
       </c>
       <c r="E57" s="3">
-        <v>242800</v>
+        <v>242100</v>
       </c>
       <c r="F57" s="3">
-        <v>237400</v>
+        <v>236800</v>
       </c>
       <c r="G57" s="3">
-        <v>459600</v>
+        <v>458300</v>
       </c>
       <c r="H57" s="3">
-        <v>420300</v>
+        <v>419200</v>
       </c>
       <c r="I57" s="3">
-        <v>408500</v>
+        <v>407400</v>
       </c>
       <c r="J57" s="3">
-        <v>488700</v>
+        <v>487300</v>
       </c>
       <c r="K57" s="3">
         <v>543900</v>
@@ -2576,25 +2576,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>294300</v>
+        <v>293500</v>
       </c>
       <c r="E58" s="3">
-        <v>455600</v>
+        <v>454300</v>
       </c>
       <c r="F58" s="3">
-        <v>544600</v>
+        <v>543100</v>
       </c>
       <c r="G58" s="3">
-        <v>667200</v>
+        <v>665400</v>
       </c>
       <c r="H58" s="3">
-        <v>52200</v>
+        <v>52000</v>
       </c>
       <c r="I58" s="3">
-        <v>70200</v>
+        <v>70100</v>
       </c>
       <c r="J58" s="3">
-        <v>1742100</v>
+        <v>1737300</v>
       </c>
       <c r="K58" s="3">
         <v>989100</v>
@@ -2618,25 +2618,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>160500</v>
+        <v>160100</v>
       </c>
       <c r="E59" s="3">
-        <v>122800</v>
+        <v>122500</v>
       </c>
       <c r="F59" s="3">
-        <v>80000</v>
+        <v>79800</v>
       </c>
       <c r="G59" s="3">
-        <v>269600</v>
+        <v>268800</v>
       </c>
       <c r="H59" s="3">
-        <v>184200</v>
+        <v>183700</v>
       </c>
       <c r="I59" s="3">
-        <v>148700</v>
+        <v>148300</v>
       </c>
       <c r="J59" s="3">
-        <v>205700</v>
+        <v>205200</v>
       </c>
       <c r="K59" s="3">
         <v>168800</v>
@@ -2702,25 +2702,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1704500</v>
+        <v>1699900</v>
       </c>
       <c r="E61" s="3">
-        <v>1239000</v>
+        <v>1235600</v>
       </c>
       <c r="F61" s="3">
-        <v>1545500</v>
+        <v>1541200</v>
       </c>
       <c r="G61" s="3">
-        <v>1194900</v>
+        <v>1191600</v>
       </c>
       <c r="H61" s="3">
-        <v>1604300</v>
+        <v>1599900</v>
       </c>
       <c r="I61" s="3">
-        <v>1650100</v>
+        <v>1645600</v>
       </c>
       <c r="J61" s="3">
-        <v>1816700</v>
+        <v>1811700</v>
       </c>
       <c r="K61" s="3">
         <v>2908400</v>
@@ -2744,25 +2744,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>29000</v>
+        <v>28900</v>
       </c>
       <c r="E62" s="3">
-        <v>71700</v>
+        <v>71500</v>
       </c>
       <c r="F62" s="3">
-        <v>59000</v>
+        <v>58800</v>
       </c>
       <c r="G62" s="3">
-        <v>74900</v>
+        <v>74700</v>
       </c>
       <c r="H62" s="3">
-        <v>61900</v>
+        <v>61700</v>
       </c>
       <c r="I62" s="3">
-        <v>70600</v>
+        <v>70400</v>
       </c>
       <c r="J62" s="3">
-        <v>59200</v>
+        <v>59100</v>
       </c>
       <c r="K62" s="3">
         <v>68000</v>
@@ -2912,25 +2912,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>99571300</v>
+        <v>99299500</v>
       </c>
       <c r="E66" s="3">
-        <v>101491000</v>
+        <v>101214000</v>
       </c>
       <c r="F66" s="3">
-        <v>98907200</v>
+        <v>98637100</v>
       </c>
       <c r="G66" s="3">
-        <v>96902400</v>
+        <v>96637800</v>
       </c>
       <c r="H66" s="3">
-        <v>94697900</v>
+        <v>94439400</v>
       </c>
       <c r="I66" s="3">
-        <v>91087500</v>
+        <v>90838800</v>
       </c>
       <c r="J66" s="3">
-        <v>87458800</v>
+        <v>87220000</v>
       </c>
       <c r="K66" s="3">
         <v>89044300</v>
@@ -3140,25 +3140,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>6818200</v>
+        <v>6799600</v>
       </c>
       <c r="E72" s="3">
-        <v>7081900</v>
+        <v>7062500</v>
       </c>
       <c r="F72" s="3">
-        <v>6751400</v>
+        <v>6732900</v>
       </c>
       <c r="G72" s="3">
-        <v>6586000</v>
+        <v>6568000</v>
       </c>
       <c r="H72" s="3">
-        <v>6524400</v>
+        <v>6506500</v>
       </c>
       <c r="I72" s="3">
-        <v>6184700</v>
+        <v>6167800</v>
       </c>
       <c r="J72" s="3">
-        <v>5400500</v>
+        <v>5385800</v>
       </c>
       <c r="K72" s="3">
         <v>5190000</v>
@@ -3308,25 +3308,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13598000</v>
+        <v>13560900</v>
       </c>
       <c r="E76" s="3">
-        <v>14837500</v>
+        <v>14797000</v>
       </c>
       <c r="F76" s="3">
-        <v>14466600</v>
+        <v>14427100</v>
       </c>
       <c r="G76" s="3">
-        <v>14007300</v>
+        <v>13969100</v>
       </c>
       <c r="H76" s="3">
-        <v>12911300</v>
+        <v>12876000</v>
       </c>
       <c r="I76" s="3">
-        <v>12610800</v>
+        <v>12576400</v>
       </c>
       <c r="J76" s="3">
-        <v>10697100</v>
+        <v>10667900</v>
       </c>
       <c r="K76" s="3">
         <v>10501500</v>
@@ -3439,25 +3439,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>468000</v>
+        <v>466700</v>
       </c>
       <c r="E81" s="3">
-        <v>571600</v>
+        <v>570000</v>
       </c>
       <c r="F81" s="3">
-        <v>361800</v>
+        <v>360800</v>
       </c>
       <c r="G81" s="3">
-        <v>330700</v>
+        <v>329800</v>
       </c>
       <c r="H81" s="3">
-        <v>743000</v>
+        <v>741000</v>
       </c>
       <c r="I81" s="3">
-        <v>1121300</v>
+        <v>1118200</v>
       </c>
       <c r="J81" s="3">
-        <v>413800</v>
+        <v>412700</v>
       </c>
       <c r="K81" s="3">
         <v>635900</v>
@@ -3499,25 +3499,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>112200</v>
+        <v>111900</v>
       </c>
       <c r="E83" s="3">
-        <v>124200</v>
+        <v>123900</v>
       </c>
       <c r="F83" s="3">
-        <v>127500</v>
+        <v>127200</v>
       </c>
       <c r="G83" s="3">
-        <v>120600</v>
+        <v>120300</v>
       </c>
       <c r="H83" s="3">
-        <v>62400</v>
+        <v>62300</v>
       </c>
       <c r="I83" s="3">
-        <v>63800</v>
+        <v>63700</v>
       </c>
       <c r="J83" s="3">
-        <v>68200</v>
+        <v>68000</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -3751,25 +3751,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>140200</v>
+        <v>139900</v>
       </c>
       <c r="E89" s="3">
-        <v>1240400</v>
+        <v>1237000</v>
       </c>
       <c r="F89" s="3">
-        <v>2264300</v>
+        <v>2258200</v>
       </c>
       <c r="G89" s="3">
-        <v>1145200</v>
+        <v>1142100</v>
       </c>
       <c r="H89" s="3">
-        <v>337800</v>
+        <v>336900</v>
       </c>
       <c r="I89" s="3">
-        <v>1623500</v>
+        <v>1619100</v>
       </c>
       <c r="J89" s="3">
-        <v>-2402700</v>
+        <v>-2396100</v>
       </c>
       <c r="K89" s="3">
         <v>-4688100</v>
@@ -3811,25 +3811,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-71100</v>
+        <v>-71000</v>
       </c>
       <c r="E91" s="3">
-        <v>-77600</v>
+        <v>-77300</v>
       </c>
       <c r="F91" s="3">
-        <v>-76800</v>
+        <v>-76600</v>
       </c>
       <c r="G91" s="3">
-        <v>-129500</v>
+        <v>-129100</v>
       </c>
       <c r="H91" s="3">
-        <v>-84200</v>
+        <v>-84000</v>
       </c>
       <c r="I91" s="3">
-        <v>-52400</v>
+        <v>-52300</v>
       </c>
       <c r="J91" s="3">
-        <v>-57400</v>
+        <v>-57300</v>
       </c>
       <c r="K91" s="3">
         <v>-38900</v>
@@ -3937,25 +3937,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>273600</v>
+        <v>272800</v>
       </c>
       <c r="E94" s="3">
-        <v>342500</v>
+        <v>341600</v>
       </c>
       <c r="F94" s="3">
-        <v>47200</v>
+        <v>47000</v>
       </c>
       <c r="G94" s="3">
         <v>-14700</v>
       </c>
       <c r="H94" s="3">
-        <v>-81100</v>
+        <v>-80900</v>
       </c>
       <c r="I94" s="3">
-        <v>535200</v>
+        <v>533700</v>
       </c>
       <c r="J94" s="3">
-        <v>231600</v>
+        <v>231000</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
@@ -3997,25 +3997,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-331200</v>
+        <v>-330300</v>
       </c>
       <c r="E96" s="3">
-        <v>-216100</v>
+        <v>-215500</v>
       </c>
       <c r="F96" s="3">
-        <v>-174100</v>
+        <v>-173600</v>
       </c>
       <c r="G96" s="3">
-        <v>-105500</v>
+        <v>-105200</v>
       </c>
       <c r="H96" s="3">
-        <v>-106700</v>
+        <v>-106400</v>
       </c>
       <c r="I96" s="3">
-        <v>-270000</v>
+        <v>-269200</v>
       </c>
       <c r="J96" s="3">
-        <v>-60000</v>
+        <v>-59800</v>
       </c>
       <c r="K96" s="3">
         <v>-126300</v>
@@ -4165,25 +4165,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1023600</v>
+        <v>-1020800</v>
       </c>
       <c r="E100" s="3">
-        <v>-847500</v>
+        <v>-845200</v>
       </c>
       <c r="F100" s="3">
-        <v>-205700</v>
+        <v>-205200</v>
       </c>
       <c r="G100" s="3">
-        <v>51800</v>
+        <v>51600</v>
       </c>
       <c r="H100" s="3">
-        <v>-327700</v>
+        <v>-326800</v>
       </c>
       <c r="I100" s="3">
-        <v>-1062400</v>
+        <v>-1059500</v>
       </c>
       <c r="J100" s="3">
-        <v>-1694200</v>
+        <v>-1689500</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>5</v>
@@ -4207,25 +4207,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-479400</v>
+        <v>-478100</v>
       </c>
       <c r="E101" s="3">
-        <v>154700</v>
+        <v>154300</v>
       </c>
       <c r="F101" s="3">
-        <v>338000</v>
+        <v>337100</v>
       </c>
       <c r="G101" s="3">
-        <v>-77600</v>
+        <v>-77300</v>
       </c>
       <c r="H101" s="3">
-        <v>-436600</v>
+        <v>-435400</v>
       </c>
       <c r="I101" s="3">
-        <v>716200</v>
+        <v>714200</v>
       </c>
       <c r="J101" s="3">
-        <v>-637500</v>
+        <v>-635700</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
@@ -4249,25 +4249,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1089200</v>
+        <v>-1086300</v>
       </c>
       <c r="E102" s="3">
-        <v>890200</v>
+        <v>887700</v>
       </c>
       <c r="F102" s="3">
-        <v>2443800</v>
+        <v>2437100</v>
       </c>
       <c r="G102" s="3">
-        <v>1104700</v>
+        <v>1101700</v>
       </c>
       <c r="H102" s="3">
-        <v>-507600</v>
+        <v>-506200</v>
       </c>
       <c r="I102" s="3">
-        <v>1812500</v>
+        <v>1807500</v>
       </c>
       <c r="J102" s="3">
-        <v>-4502700</v>
+        <v>-4490400</v>
       </c>
       <c r="K102" s="3">
         <v>-2295900</v>

--- a/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>BKEAY</t>
   </si>
@@ -656,114 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3176600</v>
+        <v>5081700</v>
       </c>
       <c r="E8" s="3">
-        <v>2308200</v>
+        <v>3181800</v>
       </c>
       <c r="F8" s="3">
-        <v>2698300</v>
+        <v>2311900</v>
       </c>
       <c r="G8" s="3">
-        <v>3653000</v>
+        <v>2702800</v>
       </c>
       <c r="H8" s="3">
-        <v>3272400</v>
+        <v>3659000</v>
       </c>
       <c r="I8" s="3">
-        <v>2765100</v>
+        <v>3277800</v>
       </c>
       <c r="J8" s="3">
+        <v>2769600</v>
+      </c>
+      <c r="K8" s="3">
         <v>2603200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3004200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3243000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3229100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2915200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2671100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -803,9 +809,12 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -845,9 +854,12 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +876,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,9 +918,12 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,9 +963,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -989,51 +1008,57 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-111900</v>
+        <v>-105000</v>
       </c>
       <c r="E15" s="3">
-        <v>-123900</v>
+        <v>-112000</v>
       </c>
       <c r="F15" s="3">
-        <v>-127200</v>
+        <v>-124100</v>
       </c>
       <c r="G15" s="3">
-        <v>-120300</v>
+        <v>-127400</v>
       </c>
       <c r="H15" s="3">
-        <v>-62300</v>
+        <v>-120500</v>
       </c>
       <c r="I15" s="3">
-        <v>-63700</v>
+        <v>-62400</v>
       </c>
       <c r="J15" s="3">
+        <v>-63800</v>
+      </c>
+      <c r="K15" s="3">
         <v>-63900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-67100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-88700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-90400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-88900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-85600</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1047,92 +1072,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2142100</v>
+        <v>3596000</v>
       </c>
       <c r="E17" s="3">
-        <v>1066300</v>
+        <v>2166300</v>
       </c>
       <c r="F17" s="3">
-        <v>1827000</v>
+        <v>1068100</v>
       </c>
       <c r="G17" s="3">
-        <v>2717800</v>
+        <v>1830000</v>
       </c>
       <c r="H17" s="3">
-        <v>1763900</v>
+        <v>2722200</v>
       </c>
       <c r="I17" s="3">
-        <v>1475100</v>
+        <v>1766800</v>
       </c>
       <c r="J17" s="3">
+        <v>1477600</v>
+      </c>
+      <c r="K17" s="3">
         <v>1627000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1743200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1754400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1721800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1690200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1495000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1034500</v>
+        <v>1485600</v>
       </c>
       <c r="E18" s="3">
-        <v>1241800</v>
+        <v>1015400</v>
       </c>
       <c r="F18" s="3">
-        <v>871400</v>
+        <v>1243900</v>
       </c>
       <c r="G18" s="3">
-        <v>935300</v>
+        <v>872800</v>
       </c>
       <c r="H18" s="3">
-        <v>1508500</v>
+        <v>936800</v>
       </c>
       <c r="I18" s="3">
-        <v>1289900</v>
+        <v>1511000</v>
       </c>
       <c r="J18" s="3">
+        <v>1292000</v>
+      </c>
+      <c r="K18" s="3">
         <v>976200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1261000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1488600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1507300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1224900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1176100</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1149,92 +1181,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-402800</v>
+        <v>-805700</v>
       </c>
       <c r="E20" s="3">
-        <v>-457400</v>
+        <v>-382700</v>
       </c>
       <c r="F20" s="3">
-        <v>-410400</v>
+        <v>-458200</v>
       </c>
       <c r="G20" s="3">
-        <v>-526400</v>
+        <v>-411000</v>
       </c>
       <c r="H20" s="3">
-        <v>-478100</v>
+        <v>-527300</v>
       </c>
       <c r="I20" s="3">
-        <v>-322800</v>
+        <v>-478900</v>
       </c>
       <c r="J20" s="3">
+        <v>-323300</v>
+      </c>
+      <c r="K20" s="3">
         <v>-389100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-447600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-415400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-414900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-250600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-439900</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>743500</v>
+        <v>784900</v>
       </c>
       <c r="E21" s="3">
-        <v>908300</v>
+        <v>744700</v>
       </c>
       <c r="F21" s="3">
-        <v>588200</v>
+        <v>909800</v>
       </c>
       <c r="G21" s="3">
-        <v>529100</v>
+        <v>589100</v>
       </c>
       <c r="H21" s="3">
-        <v>1092600</v>
+        <v>530000</v>
       </c>
       <c r="I21" s="3">
-        <v>1030800</v>
+        <v>1094400</v>
       </c>
       <c r="J21" s="3">
+        <v>1032400</v>
+      </c>
+      <c r="K21" s="3">
         <v>655000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3">
         <v>1063200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>821800</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1274,93 +1313,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>631700</v>
+        <v>679900</v>
       </c>
       <c r="E23" s="3">
-        <v>784400</v>
+        <v>632700</v>
       </c>
       <c r="F23" s="3">
-        <v>461000</v>
+        <v>785700</v>
       </c>
       <c r="G23" s="3">
-        <v>408800</v>
+        <v>461700</v>
       </c>
       <c r="H23" s="3">
-        <v>1030400</v>
+        <v>409500</v>
       </c>
       <c r="I23" s="3">
-        <v>967100</v>
+        <v>1032100</v>
       </c>
       <c r="J23" s="3">
+        <v>968700</v>
+      </c>
+      <c r="K23" s="3">
         <v>587000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>813400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1073100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1092400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>974300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>736100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>72000</v>
+        <v>150300</v>
       </c>
       <c r="E24" s="3">
-        <v>105200</v>
+        <v>72100</v>
       </c>
       <c r="F24" s="3">
+        <v>105400</v>
+      </c>
+      <c r="G24" s="3">
         <v>-10100</v>
       </c>
-      <c r="G24" s="3">
-        <v>-17600</v>
-      </c>
       <c r="H24" s="3">
-        <v>192500</v>
+        <v>-17700</v>
       </c>
       <c r="I24" s="3">
-        <v>152800</v>
+        <v>192800</v>
       </c>
       <c r="J24" s="3">
+        <v>153000</v>
+      </c>
+      <c r="K24" s="3">
         <v>136400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>133600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>210200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>229000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>181700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>166400</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1400,93 +1448,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>559700</v>
+        <v>529600</v>
       </c>
       <c r="E26" s="3">
-        <v>679200</v>
+        <v>560600</v>
       </c>
       <c r="F26" s="3">
-        <v>471100</v>
+        <v>680300</v>
       </c>
       <c r="G26" s="3">
-        <v>426500</v>
+        <v>471900</v>
       </c>
       <c r="H26" s="3">
-        <v>837900</v>
+        <v>427200</v>
       </c>
       <c r="I26" s="3">
-        <v>814300</v>
+        <v>839200</v>
       </c>
       <c r="J26" s="3">
+        <v>815700</v>
+      </c>
+      <c r="K26" s="3">
         <v>450600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>679800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>862900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>863400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>792600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>569700</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>466700</v>
+        <v>451000</v>
       </c>
       <c r="E27" s="3">
-        <v>570000</v>
+        <v>467500</v>
       </c>
       <c r="F27" s="3">
-        <v>360800</v>
+        <v>571000</v>
       </c>
       <c r="G27" s="3">
-        <v>329800</v>
+        <v>361400</v>
       </c>
       <c r="H27" s="3">
-        <v>741000</v>
+        <v>330400</v>
       </c>
       <c r="I27" s="3">
-        <v>588300</v>
+        <v>742200</v>
       </c>
       <c r="J27" s="3">
+        <v>589300</v>
+      </c>
+      <c r="K27" s="3">
         <v>373800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>597400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>806500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>808800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>737300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>515800</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1526,9 +1583,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1544,21 +1604,21 @@
       <c r="G29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
+      <c r="H29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I29" s="3">
-        <v>529900</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>530800</v>
+      </c>
+      <c r="K29" s="3">
         <v>38900</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>38500</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M29" s="3" t="s">
         <v>5</v>
       </c>
@@ -1568,9 +1628,12 @@
       <c r="O29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1610,9 +1673,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1652,93 +1718,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>402800</v>
+        <v>805700</v>
       </c>
       <c r="E32" s="3">
-        <v>457400</v>
+        <v>382700</v>
       </c>
       <c r="F32" s="3">
-        <v>410400</v>
+        <v>458200</v>
       </c>
       <c r="G32" s="3">
-        <v>526400</v>
+        <v>411000</v>
       </c>
       <c r="H32" s="3">
-        <v>478100</v>
+        <v>527300</v>
       </c>
       <c r="I32" s="3">
-        <v>322800</v>
+        <v>478900</v>
       </c>
       <c r="J32" s="3">
+        <v>323300</v>
+      </c>
+      <c r="K32" s="3">
         <v>389100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>447600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>415400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>414900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>250600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>439900</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>466700</v>
+        <v>451000</v>
       </c>
       <c r="E33" s="3">
-        <v>570000</v>
+        <v>467500</v>
       </c>
       <c r="F33" s="3">
-        <v>360800</v>
+        <v>571000</v>
       </c>
       <c r="G33" s="3">
-        <v>329800</v>
+        <v>361400</v>
       </c>
       <c r="H33" s="3">
-        <v>741000</v>
+        <v>330400</v>
       </c>
       <c r="I33" s="3">
-        <v>1118200</v>
+        <v>742200</v>
       </c>
       <c r="J33" s="3">
+        <v>1120100</v>
+      </c>
+      <c r="K33" s="3">
         <v>412700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>635900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>806500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>808800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>737300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>515800</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1778,98 +1853,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>466700</v>
+        <v>451000</v>
       </c>
       <c r="E35" s="3">
-        <v>570000</v>
+        <v>467500</v>
       </c>
       <c r="F35" s="3">
-        <v>360800</v>
+        <v>571000</v>
       </c>
       <c r="G35" s="3">
-        <v>329800</v>
+        <v>361400</v>
       </c>
       <c r="H35" s="3">
-        <v>741000</v>
+        <v>330400</v>
       </c>
       <c r="I35" s="3">
-        <v>1118200</v>
+        <v>742200</v>
       </c>
       <c r="J35" s="3">
+        <v>1120100</v>
+      </c>
+      <c r="K35" s="3">
         <v>412700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>635900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>806500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>808800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>737300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>515800</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1886,8 +1970,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1904,92 +1989,99 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6977400</v>
+        <v>5877900</v>
       </c>
       <c r="E41" s="3">
-        <v>7042400</v>
+        <v>6988800</v>
       </c>
       <c r="F41" s="3">
-        <v>7207200</v>
+        <v>7054000</v>
       </c>
       <c r="G41" s="3">
-        <v>6587000</v>
+        <v>7219100</v>
       </c>
       <c r="H41" s="3">
-        <v>6149900</v>
+        <v>6597800</v>
       </c>
       <c r="I41" s="3">
-        <v>7756100</v>
+        <v>6160000</v>
       </c>
       <c r="J41" s="3">
+        <v>7768800</v>
+      </c>
+      <c r="K41" s="3">
         <v>8390700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8810000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8969800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8854000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11013100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9185400</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>28171000</v>
+        <v>28611400</v>
       </c>
       <c r="E42" s="3">
-        <v>30539100</v>
+        <v>28217200</v>
       </c>
       <c r="F42" s="3">
-        <v>29666800</v>
+        <v>30589200</v>
       </c>
       <c r="G42" s="3">
-        <v>31300500</v>
+        <v>29715500</v>
       </c>
       <c r="H42" s="3">
-        <v>29843200</v>
+        <v>31351900</v>
       </c>
       <c r="I42" s="3">
-        <v>11519800</v>
+        <v>29892200</v>
       </c>
       <c r="J42" s="3">
+        <v>11538700</v>
+      </c>
+      <c r="K42" s="3">
         <v>9317900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>14808500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>16124900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>17747500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>14642900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>14219400</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2029,9 +2121,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2071,9 +2166,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2113,9 +2211,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2155,135 +2256,147 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1158400</v>
+        <v>1073600</v>
       </c>
       <c r="E47" s="3">
-        <v>1143800</v>
+        <v>1160300</v>
       </c>
       <c r="F47" s="3">
-        <v>1173800</v>
+        <v>1145700</v>
       </c>
       <c r="G47" s="3">
-        <v>1274600</v>
+        <v>1175800</v>
       </c>
       <c r="H47" s="3">
-        <v>1167100</v>
+        <v>1276700</v>
       </c>
       <c r="I47" s="3">
-        <v>1205400</v>
+        <v>1169000</v>
       </c>
       <c r="J47" s="3">
+        <v>1207400</v>
+      </c>
+      <c r="K47" s="3">
         <v>768400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>734200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>774900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>615200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>602400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>489000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1722800</v>
+        <v>1727800</v>
       </c>
       <c r="E48" s="3">
-        <v>1769800</v>
+        <v>1725600</v>
       </c>
       <c r="F48" s="3">
-        <v>1798100</v>
+        <v>1772700</v>
       </c>
       <c r="G48" s="3">
-        <v>1831700</v>
+        <v>1801000</v>
       </c>
       <c r="H48" s="3">
-        <v>1683000</v>
+        <v>1834700</v>
       </c>
       <c r="I48" s="3">
-        <v>1630000</v>
+        <v>1685800</v>
       </c>
       <c r="J48" s="3">
+        <v>1632600</v>
+      </c>
+      <c r="K48" s="3">
         <v>1532800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1694000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1671000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1741700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1616600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1617800</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>239100</v>
+        <v>237100</v>
       </c>
       <c r="E49" s="3">
-        <v>241000</v>
+        <v>239500</v>
       </c>
       <c r="F49" s="3">
-        <v>244400</v>
+        <v>241400</v>
       </c>
       <c r="G49" s="3">
-        <v>246200</v>
+        <v>244800</v>
       </c>
       <c r="H49" s="3">
-        <v>248000</v>
+        <v>246600</v>
       </c>
       <c r="I49" s="3">
-        <v>250400</v>
+        <v>248400</v>
       </c>
       <c r="J49" s="3">
+        <v>250800</v>
+      </c>
+      <c r="K49" s="3">
         <v>337400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>494700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>503800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>513600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>520400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>539500</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2323,9 +2436,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2365,51 +2481,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>239800</v>
+        <v>237000</v>
       </c>
       <c r="E52" s="3">
-        <v>527300</v>
+        <v>240200</v>
       </c>
       <c r="F52" s="3">
-        <v>3666300</v>
+        <v>528200</v>
       </c>
       <c r="G52" s="3">
-        <v>204800</v>
+        <v>3672300</v>
       </c>
       <c r="H52" s="3">
-        <v>149400</v>
+        <v>205100</v>
       </c>
       <c r="I52" s="3">
-        <v>136500</v>
+        <v>149700</v>
       </c>
       <c r="J52" s="3">
+        <v>136800</v>
+      </c>
+      <c r="K52" s="3">
         <v>741100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>48300</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2449,51 +2571,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>112860000</v>
+        <v>110169000</v>
       </c>
       <c r="E54" s="3">
-        <v>116011000</v>
+        <v>113046000</v>
       </c>
       <c r="F54" s="3">
-        <v>113064000</v>
+        <v>116202000</v>
       </c>
       <c r="G54" s="3">
-        <v>110607000</v>
+        <v>113250000</v>
       </c>
       <c r="H54" s="3">
-        <v>107315000</v>
+        <v>110789000</v>
       </c>
       <c r="I54" s="3">
-        <v>103415000</v>
+        <v>107492000</v>
       </c>
       <c r="J54" s="3">
+        <v>103585000</v>
+      </c>
+      <c r="K54" s="3">
         <v>97887900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>99545800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>101389000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>97056500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>89137400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>78259500</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2510,8 +2638,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2528,134 +2657,144 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>531200</v>
+        <v>674200</v>
       </c>
       <c r="E57" s="3">
-        <v>242100</v>
+        <v>532000</v>
       </c>
       <c r="F57" s="3">
-        <v>236800</v>
+        <v>242500</v>
       </c>
       <c r="G57" s="3">
-        <v>458300</v>
+        <v>237100</v>
       </c>
       <c r="H57" s="3">
-        <v>419200</v>
+        <v>459100</v>
       </c>
       <c r="I57" s="3">
-        <v>407400</v>
+        <v>419900</v>
       </c>
       <c r="J57" s="3">
+        <v>408100</v>
+      </c>
+      <c r="K57" s="3">
         <v>487300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>543900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>618200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>531800</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>293500</v>
+        <v>300500</v>
       </c>
       <c r="E58" s="3">
-        <v>454300</v>
+        <v>294000</v>
       </c>
       <c r="F58" s="3">
-        <v>543100</v>
+        <v>455100</v>
       </c>
       <c r="G58" s="3">
-        <v>665400</v>
+        <v>544000</v>
       </c>
       <c r="H58" s="3">
-        <v>52000</v>
+        <v>666500</v>
       </c>
       <c r="I58" s="3">
-        <v>70100</v>
+        <v>52100</v>
       </c>
       <c r="J58" s="3">
+        <v>70200</v>
+      </c>
+      <c r="K58" s="3">
         <v>1737300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>989100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1747800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>443900</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>437600</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>160100</v>
+        <v>205100</v>
       </c>
       <c r="E59" s="3">
-        <v>122500</v>
+        <v>160300</v>
       </c>
       <c r="F59" s="3">
-        <v>79800</v>
+        <v>122700</v>
       </c>
       <c r="G59" s="3">
-        <v>268800</v>
+        <v>79900</v>
       </c>
       <c r="H59" s="3">
-        <v>183700</v>
+        <v>269300</v>
       </c>
       <c r="I59" s="3">
-        <v>148300</v>
+        <v>184000</v>
       </c>
       <c r="J59" s="3">
+        <v>148500</v>
+      </c>
+      <c r="K59" s="3">
         <v>205200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>168800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>149300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>174200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>127200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>60500</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2695,93 +2834,102 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1699900</v>
+        <v>1961200</v>
       </c>
       <c r="E61" s="3">
-        <v>1235600</v>
+        <v>1702700</v>
       </c>
       <c r="F61" s="3">
-        <v>1541200</v>
+        <v>1237600</v>
       </c>
       <c r="G61" s="3">
-        <v>1191600</v>
+        <v>1543800</v>
       </c>
       <c r="H61" s="3">
-        <v>1599900</v>
+        <v>1193600</v>
       </c>
       <c r="I61" s="3">
-        <v>1645600</v>
+        <v>1602500</v>
       </c>
       <c r="J61" s="3">
+        <v>1648300</v>
+      </c>
+      <c r="K61" s="3">
         <v>1811700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2908400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3317100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1919600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2951900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2554400</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E62" s="3">
         <v>28900</v>
       </c>
-      <c r="E62" s="3">
-        <v>71500</v>
-      </c>
       <c r="F62" s="3">
-        <v>58800</v>
+        <v>71600</v>
       </c>
       <c r="G62" s="3">
-        <v>74700</v>
+        <v>58900</v>
       </c>
       <c r="H62" s="3">
-        <v>61700</v>
+        <v>74800</v>
       </c>
       <c r="I62" s="3">
-        <v>70400</v>
+        <v>61800</v>
       </c>
       <c r="J62" s="3">
+        <v>70600</v>
+      </c>
+      <c r="K62" s="3">
         <v>59100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>68000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>87400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>83300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>80600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>59000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2821,9 +2969,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2863,9 +3014,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2905,51 +3059,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>99299500</v>
+        <v>96331800</v>
       </c>
       <c r="E66" s="3">
-        <v>101214000</v>
+        <v>99462600</v>
       </c>
       <c r="F66" s="3">
-        <v>98637100</v>
+        <v>101380000</v>
       </c>
       <c r="G66" s="3">
-        <v>96637800</v>
+        <v>98799200</v>
       </c>
       <c r="H66" s="3">
-        <v>94439400</v>
+        <v>96796600</v>
       </c>
       <c r="I66" s="3">
-        <v>90838800</v>
+        <v>94594500</v>
       </c>
       <c r="J66" s="3">
+        <v>90988000</v>
+      </c>
+      <c r="K66" s="3">
         <v>87220000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>89044300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>92613900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>88858700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>81776600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>72164600</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2966,8 +3126,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3007,9 +3168,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3049,9 +3213,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3091,9 +3258,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3133,51 +3303,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>6799600</v>
+        <v>7042100</v>
       </c>
       <c r="E72" s="3">
-        <v>7062500</v>
+        <v>6810700</v>
       </c>
       <c r="F72" s="3">
-        <v>6732900</v>
+        <v>7074100</v>
       </c>
       <c r="G72" s="3">
-        <v>6568000</v>
+        <v>6744000</v>
       </c>
       <c r="H72" s="3">
-        <v>6506500</v>
+        <v>6578800</v>
       </c>
       <c r="I72" s="3">
-        <v>6167800</v>
+        <v>6517200</v>
       </c>
       <c r="J72" s="3">
+        <v>6177900</v>
+      </c>
+      <c r="K72" s="3">
         <v>5385800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5190000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4890600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6753700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6013600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4971100</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3217,9 +3393,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3259,9 +3438,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3301,51 +3483,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13560900</v>
+        <v>13837500</v>
       </c>
       <c r="E76" s="3">
-        <v>14797000</v>
+        <v>13583200</v>
       </c>
       <c r="F76" s="3">
-        <v>14427100</v>
+        <v>14821300</v>
       </c>
       <c r="G76" s="3">
-        <v>13969100</v>
+        <v>14450800</v>
       </c>
       <c r="H76" s="3">
-        <v>12876000</v>
+        <v>13992000</v>
       </c>
       <c r="I76" s="3">
-        <v>12576400</v>
+        <v>12897200</v>
       </c>
       <c r="J76" s="3">
+        <v>12597000</v>
+      </c>
+      <c r="K76" s="3">
         <v>10667900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10501500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8774600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8197800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7360700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6094800</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3385,98 +3573,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>466700</v>
+        <v>451000</v>
       </c>
       <c r="E81" s="3">
-        <v>570000</v>
+        <v>467500</v>
       </c>
       <c r="F81" s="3">
-        <v>360800</v>
+        <v>571000</v>
       </c>
       <c r="G81" s="3">
-        <v>329800</v>
+        <v>361400</v>
       </c>
       <c r="H81" s="3">
-        <v>741000</v>
+        <v>330400</v>
       </c>
       <c r="I81" s="3">
-        <v>1118200</v>
+        <v>742200</v>
       </c>
       <c r="J81" s="3">
+        <v>1120100</v>
+      </c>
+      <c r="K81" s="3">
         <v>412700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>635900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>806500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>808800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>737300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>515800</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3493,50 +3690,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>111900</v>
+        <v>105000</v>
       </c>
       <c r="E83" s="3">
-        <v>123900</v>
+        <v>112000</v>
       </c>
       <c r="F83" s="3">
-        <v>127200</v>
+        <v>124100</v>
       </c>
       <c r="G83" s="3">
-        <v>120300</v>
+        <v>127400</v>
       </c>
       <c r="H83" s="3">
-        <v>62300</v>
+        <v>120500</v>
       </c>
       <c r="I83" s="3">
-        <v>63700</v>
+        <v>62400</v>
       </c>
       <c r="J83" s="3">
+        <v>63800</v>
+      </c>
+      <c r="K83" s="3">
         <v>68000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
         <v>88900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>85600</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3576,9 +3777,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3618,9 +3822,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3660,9 +3867,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3702,9 +3912,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3744,51 +3957,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>139900</v>
+        <v>-2166300</v>
       </c>
       <c r="E89" s="3">
-        <v>1237000</v>
+        <v>140100</v>
       </c>
       <c r="F89" s="3">
-        <v>2258200</v>
+        <v>1239000</v>
       </c>
       <c r="G89" s="3">
-        <v>1142100</v>
+        <v>2261900</v>
       </c>
       <c r="H89" s="3">
-        <v>336900</v>
+        <v>1144000</v>
       </c>
       <c r="I89" s="3">
-        <v>1619100</v>
+        <v>337400</v>
       </c>
       <c r="J89" s="3">
+        <v>1621800</v>
+      </c>
+      <c r="K89" s="3">
         <v>-2396100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4688100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2322300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2346700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>532200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1907700</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3805,50 +4024,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-71000</v>
+        <v>-87100</v>
       </c>
       <c r="E91" s="3">
-        <v>-77300</v>
+        <v>-71100</v>
       </c>
       <c r="F91" s="3">
-        <v>-76600</v>
+        <v>-77500</v>
       </c>
       <c r="G91" s="3">
-        <v>-129100</v>
+        <v>-76700</v>
       </c>
       <c r="H91" s="3">
-        <v>-84000</v>
+        <v>-129300</v>
       </c>
       <c r="I91" s="3">
-        <v>-52300</v>
+        <v>-84100</v>
       </c>
       <c r="J91" s="3">
+        <v>-52400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-57300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-38900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-95500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-96500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-56200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-73900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3888,9 +4111,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3930,51 +4156,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>272800</v>
+        <v>-65400</v>
       </c>
       <c r="E94" s="3">
-        <v>341600</v>
+        <v>273300</v>
       </c>
       <c r="F94" s="3">
-        <v>47000</v>
+        <v>342100</v>
       </c>
       <c r="G94" s="3">
+        <v>47100</v>
+      </c>
+      <c r="H94" s="3">
         <v>-14700</v>
       </c>
-      <c r="H94" s="3">
-        <v>-80900</v>
-      </c>
       <c r="I94" s="3">
-        <v>533700</v>
+        <v>-81100</v>
       </c>
       <c r="J94" s="3">
+        <v>534600</v>
+      </c>
+      <c r="K94" s="3">
         <v>231000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
         <v>84400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>72300</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3991,50 +4223,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-330300</v>
+        <v>-176300</v>
       </c>
       <c r="E96" s="3">
-        <v>-215500</v>
+        <v>-330900</v>
       </c>
       <c r="F96" s="3">
-        <v>-173600</v>
+        <v>-215900</v>
       </c>
       <c r="G96" s="3">
-        <v>-105200</v>
+        <v>-173900</v>
       </c>
       <c r="H96" s="3">
-        <v>-106400</v>
+        <v>-105400</v>
       </c>
       <c r="I96" s="3">
-        <v>-269200</v>
+        <v>-106500</v>
       </c>
       <c r="J96" s="3">
+        <v>-269700</v>
+      </c>
+      <c r="K96" s="3">
         <v>-59800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-126300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-95200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-96200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-120000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-148100</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4074,9 +4310,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4116,9 +4355,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4158,78 +4400,84 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1020800</v>
+        <v>-223100</v>
       </c>
       <c r="E100" s="3">
-        <v>-845200</v>
+        <v>-1022500</v>
       </c>
       <c r="F100" s="3">
-        <v>-205200</v>
+        <v>-846500</v>
       </c>
       <c r="G100" s="3">
-        <v>51600</v>
+        <v>-205500</v>
       </c>
       <c r="H100" s="3">
-        <v>-326800</v>
+        <v>51700</v>
       </c>
       <c r="I100" s="3">
-        <v>-1059500</v>
+        <v>-327300</v>
       </c>
       <c r="J100" s="3">
+        <v>-1061300</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1689500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
         <v>2031000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1043700</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-478100</v>
+        <v>-108100</v>
       </c>
       <c r="E101" s="3">
-        <v>154300</v>
+        <v>-478900</v>
       </c>
       <c r="F101" s="3">
-        <v>337100</v>
+        <v>154600</v>
       </c>
       <c r="G101" s="3">
-        <v>-77300</v>
+        <v>337700</v>
       </c>
       <c r="H101" s="3">
-        <v>-435400</v>
+        <v>-77500</v>
       </c>
       <c r="I101" s="3">
-        <v>714200</v>
+        <v>-436100</v>
       </c>
       <c r="J101" s="3">
+        <v>715400</v>
+      </c>
+      <c r="K101" s="3">
         <v>-635700</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
@@ -4242,49 +4490,55 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1086300</v>
+        <v>-2562900</v>
       </c>
       <c r="E102" s="3">
-        <v>887700</v>
+        <v>-1088000</v>
       </c>
       <c r="F102" s="3">
-        <v>2437100</v>
+        <v>889200</v>
       </c>
       <c r="G102" s="3">
-        <v>1101700</v>
+        <v>2441100</v>
       </c>
       <c r="H102" s="3">
-        <v>-506200</v>
+        <v>1103500</v>
       </c>
       <c r="I102" s="3">
-        <v>1807500</v>
+        <v>-507100</v>
       </c>
       <c r="J102" s="3">
+        <v>1810500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-4490400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2295900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1239600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1252700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2647500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-791700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
@@ -729,25 +729,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5081700</v>
+        <v>5088800</v>
       </c>
       <c r="E8" s="3">
-        <v>3181800</v>
+        <v>3186300</v>
       </c>
       <c r="F8" s="3">
-        <v>2311900</v>
+        <v>2315200</v>
       </c>
       <c r="G8" s="3">
-        <v>2702800</v>
+        <v>2706600</v>
       </c>
       <c r="H8" s="3">
-        <v>3659000</v>
+        <v>3664200</v>
       </c>
       <c r="I8" s="3">
-        <v>3277800</v>
+        <v>3282400</v>
       </c>
       <c r="J8" s="3">
-        <v>2769600</v>
+        <v>2773500</v>
       </c>
       <c r="K8" s="3">
         <v>2603200</v>
@@ -1018,25 +1018,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-105000</v>
+        <v>-105100</v>
       </c>
       <c r="E15" s="3">
-        <v>-112000</v>
+        <v>-112200</v>
       </c>
       <c r="F15" s="3">
-        <v>-124100</v>
+        <v>-124300</v>
       </c>
       <c r="G15" s="3">
-        <v>-127400</v>
+        <v>-127600</v>
       </c>
       <c r="H15" s="3">
-        <v>-120500</v>
+        <v>-120700</v>
       </c>
       <c r="I15" s="3">
         <v>-62400</v>
       </c>
       <c r="J15" s="3">
-        <v>-63800</v>
+        <v>-63900</v>
       </c>
       <c r="K15" s="3">
         <v>-63900</v>
@@ -1079,25 +1079,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3596000</v>
+        <v>3601100</v>
       </c>
       <c r="E17" s="3">
-        <v>2166300</v>
+        <v>2169400</v>
       </c>
       <c r="F17" s="3">
-        <v>1068100</v>
+        <v>1069600</v>
       </c>
       <c r="G17" s="3">
-        <v>1830000</v>
+        <v>1832500</v>
       </c>
       <c r="H17" s="3">
-        <v>2722200</v>
+        <v>2726000</v>
       </c>
       <c r="I17" s="3">
-        <v>1766800</v>
+        <v>1769300</v>
       </c>
       <c r="J17" s="3">
-        <v>1477600</v>
+        <v>1479600</v>
       </c>
       <c r="K17" s="3">
         <v>1627000</v>
@@ -1124,25 +1124,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1485600</v>
+        <v>1487700</v>
       </c>
       <c r="E18" s="3">
-        <v>1015400</v>
+        <v>1016900</v>
       </c>
       <c r="F18" s="3">
-        <v>1243900</v>
+        <v>1245600</v>
       </c>
       <c r="G18" s="3">
-        <v>872800</v>
+        <v>874000</v>
       </c>
       <c r="H18" s="3">
-        <v>936800</v>
+        <v>938100</v>
       </c>
       <c r="I18" s="3">
-        <v>1511000</v>
+        <v>1513100</v>
       </c>
       <c r="J18" s="3">
-        <v>1292000</v>
+        <v>1293800</v>
       </c>
       <c r="K18" s="3">
         <v>976200</v>
@@ -1188,25 +1188,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-805700</v>
+        <v>-806800</v>
       </c>
       <c r="E20" s="3">
-        <v>-382700</v>
+        <v>-383300</v>
       </c>
       <c r="F20" s="3">
-        <v>-458200</v>
+        <v>-458800</v>
       </c>
       <c r="G20" s="3">
-        <v>-411000</v>
+        <v>-411600</v>
       </c>
       <c r="H20" s="3">
-        <v>-527300</v>
+        <v>-528100</v>
       </c>
       <c r="I20" s="3">
-        <v>-478900</v>
+        <v>-479600</v>
       </c>
       <c r="J20" s="3">
-        <v>-323300</v>
+        <v>-323800</v>
       </c>
       <c r="K20" s="3">
         <v>-389100</v>
@@ -1233,25 +1233,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>784900</v>
+        <v>786000</v>
       </c>
       <c r="E21" s="3">
-        <v>744700</v>
+        <v>745700</v>
       </c>
       <c r="F21" s="3">
-        <v>909800</v>
+        <v>911000</v>
       </c>
       <c r="G21" s="3">
-        <v>589100</v>
+        <v>589900</v>
       </c>
       <c r="H21" s="3">
-        <v>530000</v>
+        <v>530700</v>
       </c>
       <c r="I21" s="3">
-        <v>1094400</v>
+        <v>1095900</v>
       </c>
       <c r="J21" s="3">
-        <v>1032400</v>
+        <v>1033900</v>
       </c>
       <c r="K21" s="3">
         <v>655000</v>
@@ -1323,25 +1323,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>679900</v>
+        <v>680900</v>
       </c>
       <c r="E23" s="3">
-        <v>632700</v>
+        <v>633600</v>
       </c>
       <c r="F23" s="3">
-        <v>785700</v>
+        <v>786800</v>
       </c>
       <c r="G23" s="3">
-        <v>461700</v>
+        <v>462400</v>
       </c>
       <c r="H23" s="3">
-        <v>409500</v>
+        <v>410100</v>
       </c>
       <c r="I23" s="3">
-        <v>1032100</v>
+        <v>1033500</v>
       </c>
       <c r="J23" s="3">
-        <v>968700</v>
+        <v>970100</v>
       </c>
       <c r="K23" s="3">
         <v>587000</v>
@@ -1368,13 +1368,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>150300</v>
+        <v>150500</v>
       </c>
       <c r="E24" s="3">
-        <v>72100</v>
+        <v>72200</v>
       </c>
       <c r="F24" s="3">
-        <v>105400</v>
+        <v>105500</v>
       </c>
       <c r="G24" s="3">
         <v>-10100</v>
@@ -1383,10 +1383,10 @@
         <v>-17700</v>
       </c>
       <c r="I24" s="3">
-        <v>192800</v>
+        <v>193100</v>
       </c>
       <c r="J24" s="3">
-        <v>153000</v>
+        <v>153200</v>
       </c>
       <c r="K24" s="3">
         <v>136400</v>
@@ -1458,25 +1458,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>529600</v>
+        <v>530400</v>
       </c>
       <c r="E26" s="3">
-        <v>560600</v>
+        <v>561400</v>
       </c>
       <c r="F26" s="3">
-        <v>680300</v>
+        <v>681300</v>
       </c>
       <c r="G26" s="3">
-        <v>471900</v>
+        <v>472500</v>
       </c>
       <c r="H26" s="3">
-        <v>427200</v>
+        <v>427800</v>
       </c>
       <c r="I26" s="3">
-        <v>839200</v>
+        <v>840400</v>
       </c>
       <c r="J26" s="3">
-        <v>815700</v>
+        <v>816800</v>
       </c>
       <c r="K26" s="3">
         <v>450600</v>
@@ -1503,25 +1503,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>451000</v>
+        <v>451600</v>
       </c>
       <c r="E27" s="3">
-        <v>467500</v>
+        <v>468200</v>
       </c>
       <c r="F27" s="3">
-        <v>571000</v>
+        <v>571800</v>
       </c>
       <c r="G27" s="3">
-        <v>361400</v>
+        <v>361900</v>
       </c>
       <c r="H27" s="3">
-        <v>330400</v>
+        <v>330800</v>
       </c>
       <c r="I27" s="3">
-        <v>742200</v>
+        <v>743200</v>
       </c>
       <c r="J27" s="3">
-        <v>589300</v>
+        <v>590100</v>
       </c>
       <c r="K27" s="3">
         <v>373800</v>
@@ -1611,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>530800</v>
+        <v>531500</v>
       </c>
       <c r="K29" s="3">
         <v>38900</v>
@@ -1728,25 +1728,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>805700</v>
+        <v>806800</v>
       </c>
       <c r="E32" s="3">
-        <v>382700</v>
+        <v>383300</v>
       </c>
       <c r="F32" s="3">
-        <v>458200</v>
+        <v>458800</v>
       </c>
       <c r="G32" s="3">
-        <v>411000</v>
+        <v>411600</v>
       </c>
       <c r="H32" s="3">
-        <v>527300</v>
+        <v>528100</v>
       </c>
       <c r="I32" s="3">
-        <v>478900</v>
+        <v>479600</v>
       </c>
       <c r="J32" s="3">
-        <v>323300</v>
+        <v>323800</v>
       </c>
       <c r="K32" s="3">
         <v>389100</v>
@@ -1773,25 +1773,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>451000</v>
+        <v>451600</v>
       </c>
       <c r="E33" s="3">
-        <v>467500</v>
+        <v>468200</v>
       </c>
       <c r="F33" s="3">
-        <v>571000</v>
+        <v>571800</v>
       </c>
       <c r="G33" s="3">
-        <v>361400</v>
+        <v>361900</v>
       </c>
       <c r="H33" s="3">
-        <v>330400</v>
+        <v>330800</v>
       </c>
       <c r="I33" s="3">
-        <v>742200</v>
+        <v>743200</v>
       </c>
       <c r="J33" s="3">
-        <v>1120100</v>
+        <v>1121600</v>
       </c>
       <c r="K33" s="3">
         <v>412700</v>
@@ -1863,25 +1863,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>451000</v>
+        <v>451600</v>
       </c>
       <c r="E35" s="3">
-        <v>467500</v>
+        <v>468200</v>
       </c>
       <c r="F35" s="3">
-        <v>571000</v>
+        <v>571800</v>
       </c>
       <c r="G35" s="3">
-        <v>361400</v>
+        <v>361900</v>
       </c>
       <c r="H35" s="3">
-        <v>330400</v>
+        <v>330800</v>
       </c>
       <c r="I35" s="3">
-        <v>742200</v>
+        <v>743200</v>
       </c>
       <c r="J35" s="3">
-        <v>1120100</v>
+        <v>1121600</v>
       </c>
       <c r="K35" s="3">
         <v>412700</v>
@@ -1996,25 +1996,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5877900</v>
+        <v>5886100</v>
       </c>
       <c r="E41" s="3">
-        <v>6988800</v>
+        <v>6998700</v>
       </c>
       <c r="F41" s="3">
-        <v>7054000</v>
+        <v>7063900</v>
       </c>
       <c r="G41" s="3">
-        <v>7219100</v>
+        <v>7229200</v>
       </c>
       <c r="H41" s="3">
-        <v>6597800</v>
+        <v>6607100</v>
       </c>
       <c r="I41" s="3">
-        <v>6160000</v>
+        <v>6168600</v>
       </c>
       <c r="J41" s="3">
-        <v>7768800</v>
+        <v>7779700</v>
       </c>
       <c r="K41" s="3">
         <v>8390700</v>
@@ -2041,25 +2041,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>28611400</v>
+        <v>28651600</v>
       </c>
       <c r="E42" s="3">
-        <v>28217200</v>
+        <v>28256900</v>
       </c>
       <c r="F42" s="3">
-        <v>30589200</v>
+        <v>30632200</v>
       </c>
       <c r="G42" s="3">
-        <v>29715500</v>
+        <v>29757300</v>
       </c>
       <c r="H42" s="3">
-        <v>31351900</v>
+        <v>31396000</v>
       </c>
       <c r="I42" s="3">
-        <v>29892200</v>
+        <v>29934300</v>
       </c>
       <c r="J42" s="3">
-        <v>11538700</v>
+        <v>11554900</v>
       </c>
       <c r="K42" s="3">
         <v>9317900</v>
@@ -2266,25 +2266,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1073600</v>
+        <v>1075100</v>
       </c>
       <c r="E47" s="3">
-        <v>1160300</v>
+        <v>1161900</v>
       </c>
       <c r="F47" s="3">
-        <v>1145700</v>
+        <v>1147300</v>
       </c>
       <c r="G47" s="3">
-        <v>1175800</v>
+        <v>1177400</v>
       </c>
       <c r="H47" s="3">
-        <v>1276700</v>
+        <v>1278500</v>
       </c>
       <c r="I47" s="3">
-        <v>1169000</v>
+        <v>1170600</v>
       </c>
       <c r="J47" s="3">
-        <v>1207400</v>
+        <v>1209100</v>
       </c>
       <c r="K47" s="3">
         <v>768400</v>
@@ -2311,25 +2311,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1727800</v>
+        <v>1730200</v>
       </c>
       <c r="E48" s="3">
-        <v>1725600</v>
+        <v>1728000</v>
       </c>
       <c r="F48" s="3">
-        <v>1772700</v>
+        <v>1775200</v>
       </c>
       <c r="G48" s="3">
-        <v>1801000</v>
+        <v>1803600</v>
       </c>
       <c r="H48" s="3">
-        <v>1834700</v>
+        <v>1837300</v>
       </c>
       <c r="I48" s="3">
-        <v>1685800</v>
+        <v>1688100</v>
       </c>
       <c r="J48" s="3">
-        <v>1632600</v>
+        <v>1634900</v>
       </c>
       <c r="K48" s="3">
         <v>1532800</v>
@@ -2356,25 +2356,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>237100</v>
+        <v>237500</v>
       </c>
       <c r="E49" s="3">
-        <v>239500</v>
+        <v>239800</v>
       </c>
       <c r="F49" s="3">
-        <v>241400</v>
+        <v>241700</v>
       </c>
       <c r="G49" s="3">
-        <v>244800</v>
+        <v>245200</v>
       </c>
       <c r="H49" s="3">
-        <v>246600</v>
+        <v>247000</v>
       </c>
       <c r="I49" s="3">
-        <v>248400</v>
+        <v>248800</v>
       </c>
       <c r="J49" s="3">
-        <v>250800</v>
+        <v>251200</v>
       </c>
       <c r="K49" s="3">
         <v>337400</v>
@@ -2491,25 +2491,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>237000</v>
+        <v>237400</v>
       </c>
       <c r="E52" s="3">
-        <v>240200</v>
+        <v>240600</v>
       </c>
       <c r="F52" s="3">
-        <v>528200</v>
+        <v>528900</v>
       </c>
       <c r="G52" s="3">
-        <v>3672300</v>
+        <v>3677500</v>
       </c>
       <c r="H52" s="3">
-        <v>205100</v>
+        <v>205400</v>
       </c>
       <c r="I52" s="3">
-        <v>149700</v>
+        <v>149900</v>
       </c>
       <c r="J52" s="3">
-        <v>136800</v>
+        <v>136900</v>
       </c>
       <c r="K52" s="3">
         <v>741100</v>
@@ -2581,25 +2581,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>110169000</v>
+        <v>110324000</v>
       </c>
       <c r="E54" s="3">
-        <v>113046000</v>
+        <v>113205000</v>
       </c>
       <c r="F54" s="3">
-        <v>116202000</v>
+        <v>116365000</v>
       </c>
       <c r="G54" s="3">
-        <v>113250000</v>
+        <v>113409000</v>
       </c>
       <c r="H54" s="3">
-        <v>110789000</v>
+        <v>110944000</v>
       </c>
       <c r="I54" s="3">
-        <v>107492000</v>
+        <v>107643000</v>
       </c>
       <c r="J54" s="3">
-        <v>103585000</v>
+        <v>103731000</v>
       </c>
       <c r="K54" s="3">
         <v>97887900</v>
@@ -2664,25 +2664,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>674200</v>
+        <v>675100</v>
       </c>
       <c r="E57" s="3">
-        <v>532000</v>
+        <v>532800</v>
       </c>
       <c r="F57" s="3">
-        <v>242500</v>
+        <v>242900</v>
       </c>
       <c r="G57" s="3">
-        <v>237100</v>
+        <v>237500</v>
       </c>
       <c r="H57" s="3">
-        <v>459100</v>
+        <v>459700</v>
       </c>
       <c r="I57" s="3">
-        <v>419900</v>
+        <v>420500</v>
       </c>
       <c r="J57" s="3">
-        <v>408100</v>
+        <v>408700</v>
       </c>
       <c r="K57" s="3">
         <v>487300</v>
@@ -2709,25 +2709,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300500</v>
+        <v>301000</v>
       </c>
       <c r="E58" s="3">
-        <v>294000</v>
+        <v>294400</v>
       </c>
       <c r="F58" s="3">
-        <v>455100</v>
+        <v>455700</v>
       </c>
       <c r="G58" s="3">
-        <v>544000</v>
+        <v>544700</v>
       </c>
       <c r="H58" s="3">
-        <v>666500</v>
+        <v>667400</v>
       </c>
       <c r="I58" s="3">
-        <v>52100</v>
+        <v>52200</v>
       </c>
       <c r="J58" s="3">
-        <v>70200</v>
+        <v>70300</v>
       </c>
       <c r="K58" s="3">
         <v>1737300</v>
@@ -2754,25 +2754,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>205100</v>
+        <v>205400</v>
       </c>
       <c r="E59" s="3">
-        <v>160300</v>
+        <v>160500</v>
       </c>
       <c r="F59" s="3">
-        <v>122700</v>
+        <v>122800</v>
       </c>
       <c r="G59" s="3">
-        <v>79900</v>
+        <v>80000</v>
       </c>
       <c r="H59" s="3">
-        <v>269300</v>
+        <v>269700</v>
       </c>
       <c r="I59" s="3">
-        <v>184000</v>
+        <v>184300</v>
       </c>
       <c r="J59" s="3">
-        <v>148500</v>
+        <v>148700</v>
       </c>
       <c r="K59" s="3">
         <v>205200</v>
@@ -2844,25 +2844,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1961200</v>
+        <v>1964000</v>
       </c>
       <c r="E61" s="3">
-        <v>1702700</v>
+        <v>1705100</v>
       </c>
       <c r="F61" s="3">
-        <v>1237600</v>
+        <v>1239300</v>
       </c>
       <c r="G61" s="3">
-        <v>1543800</v>
+        <v>1545900</v>
       </c>
       <c r="H61" s="3">
-        <v>1193600</v>
+        <v>1195200</v>
       </c>
       <c r="I61" s="3">
-        <v>1602500</v>
+        <v>1604800</v>
       </c>
       <c r="J61" s="3">
-        <v>1648300</v>
+        <v>1650600</v>
       </c>
       <c r="K61" s="3">
         <v>1811700</v>
@@ -2889,25 +2889,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>59900</v>
+        <v>60000</v>
       </c>
       <c r="E62" s="3">
-        <v>28900</v>
+        <v>29000</v>
       </c>
       <c r="F62" s="3">
-        <v>71600</v>
+        <v>71700</v>
       </c>
       <c r="G62" s="3">
-        <v>58900</v>
+        <v>59000</v>
       </c>
       <c r="H62" s="3">
-        <v>74800</v>
+        <v>74900</v>
       </c>
       <c r="I62" s="3">
-        <v>61800</v>
+        <v>61900</v>
       </c>
       <c r="J62" s="3">
-        <v>70600</v>
+        <v>70700</v>
       </c>
       <c r="K62" s="3">
         <v>59100</v>
@@ -3069,25 +3069,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>96331800</v>
+        <v>96467200</v>
       </c>
       <c r="E66" s="3">
-        <v>99462600</v>
+        <v>99602400</v>
       </c>
       <c r="F66" s="3">
-        <v>101380000</v>
+        <v>101523000</v>
       </c>
       <c r="G66" s="3">
-        <v>98799200</v>
+        <v>98938000</v>
       </c>
       <c r="H66" s="3">
-        <v>96796600</v>
+        <v>96932600</v>
       </c>
       <c r="I66" s="3">
-        <v>94594500</v>
+        <v>94727500</v>
       </c>
       <c r="J66" s="3">
-        <v>90988000</v>
+        <v>91115900</v>
       </c>
       <c r="K66" s="3">
         <v>87220000</v>
@@ -3313,25 +3313,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7042100</v>
+        <v>7052000</v>
       </c>
       <c r="E72" s="3">
-        <v>6810700</v>
+        <v>6820300</v>
       </c>
       <c r="F72" s="3">
-        <v>7074100</v>
+        <v>7084100</v>
       </c>
       <c r="G72" s="3">
-        <v>6744000</v>
+        <v>6753500</v>
       </c>
       <c r="H72" s="3">
-        <v>6578800</v>
+        <v>6588100</v>
       </c>
       <c r="I72" s="3">
-        <v>6517200</v>
+        <v>6526400</v>
       </c>
       <c r="J72" s="3">
-        <v>6177900</v>
+        <v>6186600</v>
       </c>
       <c r="K72" s="3">
         <v>5385800</v>
@@ -3493,25 +3493,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13837500</v>
+        <v>13856900</v>
       </c>
       <c r="E76" s="3">
-        <v>13583200</v>
+        <v>13602300</v>
       </c>
       <c r="F76" s="3">
-        <v>14821300</v>
+        <v>14842100</v>
       </c>
       <c r="G76" s="3">
-        <v>14450800</v>
+        <v>14471100</v>
       </c>
       <c r="H76" s="3">
-        <v>13992000</v>
+        <v>14011700</v>
       </c>
       <c r="I76" s="3">
-        <v>12897200</v>
+        <v>12915300</v>
       </c>
       <c r="J76" s="3">
-        <v>12597000</v>
+        <v>12614800</v>
       </c>
       <c r="K76" s="3">
         <v>10667900</v>
@@ -3633,25 +3633,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>451000</v>
+        <v>451600</v>
       </c>
       <c r="E81" s="3">
-        <v>467500</v>
+        <v>468200</v>
       </c>
       <c r="F81" s="3">
-        <v>571000</v>
+        <v>571800</v>
       </c>
       <c r="G81" s="3">
-        <v>361400</v>
+        <v>361900</v>
       </c>
       <c r="H81" s="3">
-        <v>330400</v>
+        <v>330800</v>
       </c>
       <c r="I81" s="3">
-        <v>742200</v>
+        <v>743200</v>
       </c>
       <c r="J81" s="3">
-        <v>1120100</v>
+        <v>1121600</v>
       </c>
       <c r="K81" s="3">
         <v>412700</v>
@@ -3697,25 +3697,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>105000</v>
+        <v>105100</v>
       </c>
       <c r="E83" s="3">
-        <v>112000</v>
+        <v>112200</v>
       </c>
       <c r="F83" s="3">
-        <v>124100</v>
+        <v>124300</v>
       </c>
       <c r="G83" s="3">
-        <v>127400</v>
+        <v>127600</v>
       </c>
       <c r="H83" s="3">
-        <v>120500</v>
+        <v>120700</v>
       </c>
       <c r="I83" s="3">
         <v>62400</v>
       </c>
       <c r="J83" s="3">
-        <v>63800</v>
+        <v>63900</v>
       </c>
       <c r="K83" s="3">
         <v>68000</v>
@@ -3967,25 +3967,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-2166300</v>
+        <v>-2169400</v>
       </c>
       <c r="E89" s="3">
-        <v>140100</v>
+        <v>140300</v>
       </c>
       <c r="F89" s="3">
-        <v>1239000</v>
+        <v>1240800</v>
       </c>
       <c r="G89" s="3">
-        <v>2261900</v>
+        <v>2265100</v>
       </c>
       <c r="H89" s="3">
-        <v>1144000</v>
+        <v>1145600</v>
       </c>
       <c r="I89" s="3">
-        <v>337400</v>
+        <v>337900</v>
       </c>
       <c r="J89" s="3">
-        <v>1621800</v>
+        <v>1624000</v>
       </c>
       <c r="K89" s="3">
         <v>-2396100</v>
@@ -4031,22 +4031,22 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-87100</v>
+        <v>-87200</v>
       </c>
       <c r="E91" s="3">
-        <v>-71100</v>
+        <v>-71200</v>
       </c>
       <c r="F91" s="3">
-        <v>-77500</v>
+        <v>-77600</v>
       </c>
       <c r="G91" s="3">
-        <v>-76700</v>
+        <v>-76800</v>
       </c>
       <c r="H91" s="3">
-        <v>-129300</v>
+        <v>-129500</v>
       </c>
       <c r="I91" s="3">
-        <v>-84100</v>
+        <v>-84200</v>
       </c>
       <c r="J91" s="3">
         <v>-52400</v>
@@ -4166,25 +4166,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-65400</v>
+        <v>-65500</v>
       </c>
       <c r="E94" s="3">
-        <v>273300</v>
+        <v>273600</v>
       </c>
       <c r="F94" s="3">
-        <v>342100</v>
+        <v>342600</v>
       </c>
       <c r="G94" s="3">
-        <v>47100</v>
+        <v>47200</v>
       </c>
       <c r="H94" s="3">
         <v>-14700</v>
       </c>
       <c r="I94" s="3">
-        <v>-81100</v>
+        <v>-81200</v>
       </c>
       <c r="J94" s="3">
-        <v>534600</v>
+        <v>535400</v>
       </c>
       <c r="K94" s="3">
         <v>231000</v>
@@ -4230,25 +4230,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-176300</v>
+        <v>-176600</v>
       </c>
       <c r="E96" s="3">
-        <v>-330900</v>
+        <v>-331300</v>
       </c>
       <c r="F96" s="3">
-        <v>-215900</v>
+        <v>-216200</v>
       </c>
       <c r="G96" s="3">
-        <v>-173900</v>
+        <v>-174100</v>
       </c>
       <c r="H96" s="3">
-        <v>-105400</v>
+        <v>-105500</v>
       </c>
       <c r="I96" s="3">
-        <v>-106500</v>
+        <v>-106700</v>
       </c>
       <c r="J96" s="3">
-        <v>-269700</v>
+        <v>-270100</v>
       </c>
       <c r="K96" s="3">
         <v>-59800</v>
@@ -4410,25 +4410,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-223100</v>
+        <v>-223400</v>
       </c>
       <c r="E100" s="3">
-        <v>-1022500</v>
+        <v>-1023900</v>
       </c>
       <c r="F100" s="3">
-        <v>-846500</v>
+        <v>-847700</v>
       </c>
       <c r="G100" s="3">
-        <v>-205500</v>
+        <v>-205800</v>
       </c>
       <c r="H100" s="3">
-        <v>51700</v>
+        <v>51800</v>
       </c>
       <c r="I100" s="3">
-        <v>-327300</v>
+        <v>-327800</v>
       </c>
       <c r="J100" s="3">
-        <v>-1061300</v>
+        <v>-1062800</v>
       </c>
       <c r="K100" s="3">
         <v>-1689500</v>
@@ -4455,25 +4455,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-108100</v>
+        <v>-108200</v>
       </c>
       <c r="E101" s="3">
-        <v>-478900</v>
+        <v>-479600</v>
       </c>
       <c r="F101" s="3">
-        <v>154600</v>
+        <v>154800</v>
       </c>
       <c r="G101" s="3">
-        <v>337700</v>
+        <v>338100</v>
       </c>
       <c r="H101" s="3">
-        <v>-77500</v>
+        <v>-77600</v>
       </c>
       <c r="I101" s="3">
-        <v>-436100</v>
+        <v>-436800</v>
       </c>
       <c r="J101" s="3">
-        <v>715400</v>
+        <v>716400</v>
       </c>
       <c r="K101" s="3">
         <v>-635700</v>
@@ -4500,25 +4500,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2562900</v>
+        <v>-2566500</v>
       </c>
       <c r="E102" s="3">
-        <v>-1088000</v>
+        <v>-1089600</v>
       </c>
       <c r="F102" s="3">
-        <v>889200</v>
+        <v>890400</v>
       </c>
       <c r="G102" s="3">
-        <v>2441100</v>
+        <v>2444600</v>
       </c>
       <c r="H102" s="3">
-        <v>1103500</v>
+        <v>1105100</v>
       </c>
       <c r="I102" s="3">
-        <v>-507100</v>
+        <v>-507800</v>
       </c>
       <c r="J102" s="3">
-        <v>1810500</v>
+        <v>1813000</v>
       </c>
       <c r="K102" s="3">
         <v>-4490400</v>

--- a/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>BKEAY</t>
   </si>
@@ -729,25 +729,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5088800</v>
+        <v>1861400</v>
       </c>
       <c r="E8" s="3">
-        <v>3186300</v>
+        <v>1729300</v>
       </c>
       <c r="F8" s="3">
-        <v>2315200</v>
+        <v>2029200</v>
       </c>
       <c r="G8" s="3">
-        <v>2706600</v>
+        <v>1587700</v>
       </c>
       <c r="H8" s="3">
-        <v>3664200</v>
+        <v>1604800</v>
       </c>
       <c r="I8" s="3">
-        <v>3282400</v>
+        <v>1991600</v>
       </c>
       <c r="J8" s="3">
-        <v>2773500</v>
+        <v>1975400</v>
       </c>
       <c r="K8" s="3">
         <v>2603200</v>
@@ -818,26 +818,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>1861400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1729300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2029200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1587700</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1604800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1991600</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1975400</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -973,25 +973,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>21700</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>16300</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-58700</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>24400</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1018,25 +1018,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-105100</v>
+        <v>71700</v>
       </c>
       <c r="E15" s="3">
-        <v>-112200</v>
+        <v>74400</v>
       </c>
       <c r="F15" s="3">
-        <v>-124300</v>
+        <v>76300</v>
       </c>
       <c r="G15" s="3">
-        <v>-127600</v>
+        <v>73500</v>
       </c>
       <c r="H15" s="3">
-        <v>-120700</v>
+        <v>69800</v>
       </c>
       <c r="I15" s="3">
-        <v>-62400</v>
+        <v>62200</v>
       </c>
       <c r="J15" s="3">
-        <v>-63900</v>
+        <v>63700</v>
       </c>
       <c r="K15" s="3">
         <v>-63900</v>
@@ -1079,25 +1079,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3601100</v>
+        <v>1206500</v>
       </c>
       <c r="E17" s="3">
-        <v>2169400</v>
+        <v>1181900</v>
       </c>
       <c r="F17" s="3">
-        <v>1069600</v>
+        <v>1194200</v>
       </c>
       <c r="G17" s="3">
-        <v>1832500</v>
+        <v>1154200</v>
       </c>
       <c r="H17" s="3">
-        <v>2726000</v>
+        <v>1268100</v>
       </c>
       <c r="I17" s="3">
-        <v>1769300</v>
+        <v>1091600</v>
       </c>
       <c r="J17" s="3">
-        <v>1479600</v>
+        <v>1027800</v>
       </c>
       <c r="K17" s="3">
         <v>1627000</v>
@@ -1124,25 +1124,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1487700</v>
+        <v>654900</v>
       </c>
       <c r="E18" s="3">
-        <v>1016900</v>
+        <v>547400</v>
       </c>
       <c r="F18" s="3">
-        <v>1245600</v>
+        <v>835000</v>
       </c>
       <c r="G18" s="3">
-        <v>874000</v>
+        <v>433500</v>
       </c>
       <c r="H18" s="3">
-        <v>938100</v>
+        <v>336800</v>
       </c>
       <c r="I18" s="3">
-        <v>1513100</v>
+        <v>900000</v>
       </c>
       <c r="J18" s="3">
-        <v>1293800</v>
+        <v>947600</v>
       </c>
       <c r="K18" s="3">
         <v>976200</v>
@@ -1188,25 +1188,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-806800</v>
+        <v>-35800</v>
       </c>
       <c r="E20" s="3">
-        <v>-383300</v>
+        <v>-108000</v>
       </c>
       <c r="F20" s="3">
-        <v>-458800</v>
+        <v>31800</v>
       </c>
       <c r="G20" s="3">
-        <v>-411600</v>
+        <v>-38200</v>
       </c>
       <c r="H20" s="3">
-        <v>-528100</v>
+        <v>-78100</v>
       </c>
       <c r="I20" s="3">
-        <v>-479600</v>
+        <v>-70500</v>
       </c>
       <c r="J20" s="3">
-        <v>-323800</v>
+        <v>-45100</v>
       </c>
       <c r="K20" s="3">
         <v>-389100</v>
@@ -1233,25 +1233,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>786000</v>
+        <v>762400</v>
       </c>
       <c r="E21" s="3">
-        <v>745700</v>
+        <v>729700</v>
       </c>
       <c r="F21" s="3">
-        <v>911000</v>
+        <v>879500</v>
       </c>
       <c r="G21" s="3">
-        <v>589900</v>
+        <v>545200</v>
       </c>
       <c r="H21" s="3">
-        <v>530700</v>
+        <v>484700</v>
       </c>
       <c r="I21" s="3">
-        <v>1095900</v>
+        <v>1032600</v>
       </c>
       <c r="J21" s="3">
-        <v>1033900</v>
+        <v>1056400</v>
       </c>
       <c r="K21" s="3">
         <v>655000</v>
@@ -1277,26 +1277,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1323,25 +1323,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>680900</v>
+        <v>679700</v>
       </c>
       <c r="E23" s="3">
-        <v>633600</v>
+        <v>633700</v>
       </c>
       <c r="F23" s="3">
-        <v>786800</v>
+        <v>786900</v>
       </c>
       <c r="G23" s="3">
-        <v>462400</v>
+        <v>465100</v>
       </c>
       <c r="H23" s="3">
-        <v>410100</v>
+        <v>410600</v>
       </c>
       <c r="I23" s="3">
-        <v>1033500</v>
+        <v>1029200</v>
       </c>
       <c r="J23" s="3">
-        <v>970100</v>
+        <v>968200</v>
       </c>
       <c r="K23" s="3">
         <v>587000</v>
@@ -1368,7 +1368,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>150500</v>
+        <v>150300</v>
       </c>
       <c r="E24" s="3">
         <v>72200</v>
@@ -1377,16 +1377,16 @@
         <v>105500</v>
       </c>
       <c r="G24" s="3">
-        <v>-10100</v>
+        <v>-10200</v>
       </c>
       <c r="H24" s="3">
         <v>-17700</v>
       </c>
       <c r="I24" s="3">
-        <v>193100</v>
+        <v>192300</v>
       </c>
       <c r="J24" s="3">
-        <v>153200</v>
+        <v>152900</v>
       </c>
       <c r="K24" s="3">
         <v>136400</v>
@@ -1458,25 +1458,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>530400</v>
+        <v>529500</v>
       </c>
       <c r="E26" s="3">
-        <v>561400</v>
+        <v>561500</v>
       </c>
       <c r="F26" s="3">
-        <v>681300</v>
+        <v>681400</v>
       </c>
       <c r="G26" s="3">
-        <v>472500</v>
+        <v>475300</v>
       </c>
       <c r="H26" s="3">
-        <v>427800</v>
+        <v>428300</v>
       </c>
       <c r="I26" s="3">
-        <v>840400</v>
+        <v>836900</v>
       </c>
       <c r="J26" s="3">
-        <v>816800</v>
+        <v>815300</v>
       </c>
       <c r="K26" s="3">
         <v>450600</v>
@@ -1503,7 +1503,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>451600</v>
+        <v>450900</v>
       </c>
       <c r="E27" s="3">
         <v>468200</v>
@@ -1512,16 +1512,16 @@
         <v>571800</v>
       </c>
       <c r="G27" s="3">
-        <v>361900</v>
+        <v>364000</v>
       </c>
       <c r="H27" s="3">
-        <v>330800</v>
+        <v>331200</v>
       </c>
       <c r="I27" s="3">
-        <v>743200</v>
+        <v>740100</v>
       </c>
       <c r="J27" s="3">
-        <v>590100</v>
+        <v>1119500</v>
       </c>
       <c r="K27" s="3">
         <v>373800</v>
@@ -1592,26 +1592,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>531500</v>
+        <v>530500</v>
       </c>
       <c r="K29" s="3">
         <v>38900</v>
@@ -1728,25 +1728,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>806800</v>
+        <v>35800</v>
       </c>
       <c r="E32" s="3">
-        <v>383300</v>
+        <v>108000</v>
       </c>
       <c r="F32" s="3">
-        <v>458800</v>
+        <v>-31800</v>
       </c>
       <c r="G32" s="3">
-        <v>411600</v>
+        <v>38200</v>
       </c>
       <c r="H32" s="3">
-        <v>528100</v>
+        <v>78100</v>
       </c>
       <c r="I32" s="3">
-        <v>479600</v>
+        <v>70500</v>
       </c>
       <c r="J32" s="3">
-        <v>323800</v>
+        <v>45100</v>
       </c>
       <c r="K32" s="3">
         <v>389100</v>
@@ -1773,25 +1773,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>451600</v>
+        <v>527100</v>
       </c>
       <c r="E33" s="3">
-        <v>468200</v>
+        <v>559000</v>
       </c>
       <c r="F33" s="3">
-        <v>571800</v>
+        <v>675800</v>
       </c>
       <c r="G33" s="3">
-        <v>361900</v>
+        <v>466100</v>
       </c>
       <c r="H33" s="3">
-        <v>330800</v>
+        <v>418500</v>
       </c>
       <c r="I33" s="3">
-        <v>743200</v>
+        <v>831100</v>
       </c>
       <c r="J33" s="3">
-        <v>1121600</v>
+        <v>1196300</v>
       </c>
       <c r="K33" s="3">
         <v>412700</v>
@@ -1863,25 +1863,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>451600</v>
+        <v>527100</v>
       </c>
       <c r="E35" s="3">
-        <v>468200</v>
+        <v>559000</v>
       </c>
       <c r="F35" s="3">
-        <v>571800</v>
+        <v>675800</v>
       </c>
       <c r="G35" s="3">
-        <v>361900</v>
+        <v>466100</v>
       </c>
       <c r="H35" s="3">
-        <v>330800</v>
+        <v>418500</v>
       </c>
       <c r="I35" s="3">
-        <v>743200</v>
+        <v>831100</v>
       </c>
       <c r="J35" s="3">
-        <v>1121600</v>
+        <v>1196300</v>
       </c>
       <c r="K35" s="3">
         <v>412700</v>
@@ -1996,25 +1996,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5886100</v>
+        <v>11709800</v>
       </c>
       <c r="E41" s="3">
-        <v>6998700</v>
+        <v>13398600</v>
       </c>
       <c r="F41" s="3">
-        <v>7063900</v>
+        <v>15471200</v>
       </c>
       <c r="G41" s="3">
-        <v>7229200</v>
+        <v>14662100</v>
       </c>
       <c r="H41" s="3">
-        <v>6607100</v>
+        <v>12148900</v>
       </c>
       <c r="I41" s="3">
-        <v>6168600</v>
+        <v>10771400</v>
       </c>
       <c r="J41" s="3">
-        <v>7779700</v>
+        <v>10856800</v>
       </c>
       <c r="K41" s="3">
         <v>8390700</v>
@@ -2041,25 +2041,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>28651600</v>
+        <v>2154500</v>
       </c>
       <c r="E42" s="3">
-        <v>28256900</v>
+        <v>1707900</v>
       </c>
       <c r="F42" s="3">
-        <v>30632200</v>
+        <v>1056700</v>
       </c>
       <c r="G42" s="3">
-        <v>29757300</v>
+        <v>1722900</v>
       </c>
       <c r="H42" s="3">
-        <v>31396000</v>
+        <v>3524900</v>
       </c>
       <c r="I42" s="3">
-        <v>29934300</v>
+        <v>2577700</v>
       </c>
       <c r="J42" s="3">
-        <v>11554900</v>
+        <v>2797900</v>
       </c>
       <c r="K42" s="3">
         <v>9317900</v>
@@ -2085,26 +2085,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2131,25 +2131,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>218100</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>53400</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>30800</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>28900</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>18800</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>190100</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2176,25 +2176,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>3929200</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>3993800</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>4290400</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>5970700</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>3131400</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>3270200</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>2730800</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2221,25 +2221,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>19149600</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>20490400</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>22366800</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>24111100</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>20778600</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>19183200</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>20197400</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2266,25 +2266,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1075100</v>
+        <v>20501800</v>
       </c>
       <c r="E47" s="3">
-        <v>1161900</v>
+        <v>19911900</v>
       </c>
       <c r="F47" s="3">
-        <v>1147300</v>
+        <v>19414400</v>
       </c>
       <c r="G47" s="3">
-        <v>1177400</v>
+        <v>18755700</v>
       </c>
       <c r="H47" s="3">
-        <v>1278500</v>
+        <v>20159400</v>
       </c>
       <c r="I47" s="3">
-        <v>1170600</v>
+        <v>19352800</v>
       </c>
       <c r="J47" s="3">
-        <v>1209100</v>
+        <v>18101500</v>
       </c>
       <c r="K47" s="3">
         <v>768400</v>
@@ -2311,25 +2311,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1730200</v>
+        <v>1073800</v>
       </c>
       <c r="E48" s="3">
-        <v>1728000</v>
+        <v>1065800</v>
       </c>
       <c r="F48" s="3">
-        <v>1775200</v>
+        <v>1135200</v>
       </c>
       <c r="G48" s="3">
-        <v>1803600</v>
+        <v>1174200</v>
       </c>
       <c r="H48" s="3">
-        <v>1837300</v>
+        <v>1154800</v>
       </c>
       <c r="I48" s="3">
-        <v>1688100</v>
+        <v>1010800</v>
       </c>
       <c r="J48" s="3">
-        <v>1634900</v>
+        <v>978200</v>
       </c>
       <c r="K48" s="3">
         <v>1532800</v>
@@ -2356,7 +2356,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>237500</v>
+        <v>237100</v>
       </c>
       <c r="E49" s="3">
         <v>239800</v>
@@ -2365,16 +2365,16 @@
         <v>241700</v>
       </c>
       <c r="G49" s="3">
-        <v>245200</v>
+        <v>246600</v>
       </c>
       <c r="H49" s="3">
-        <v>247000</v>
+        <v>247300</v>
       </c>
       <c r="I49" s="3">
-        <v>248800</v>
+        <v>247700</v>
       </c>
       <c r="J49" s="3">
-        <v>251200</v>
+        <v>250700</v>
       </c>
       <c r="K49" s="3">
         <v>337400</v>
@@ -2491,25 +2491,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>237400</v>
+        <v>1430800</v>
       </c>
       <c r="E52" s="3">
-        <v>240600</v>
+        <v>1647200</v>
       </c>
       <c r="F52" s="3">
-        <v>528900</v>
+        <v>1778100</v>
       </c>
       <c r="G52" s="3">
-        <v>3677500</v>
+        <v>2342100</v>
       </c>
       <c r="H52" s="3">
-        <v>205400</v>
+        <v>2108800</v>
       </c>
       <c r="I52" s="3">
-        <v>149900</v>
+        <v>1838300</v>
       </c>
       <c r="J52" s="3">
-        <v>136900</v>
+        <v>1951000</v>
       </c>
       <c r="K52" s="3">
         <v>741100</v>
@@ -2581,25 +2581,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>110324000</v>
+        <v>110135400</v>
       </c>
       <c r="E54" s="3">
-        <v>113205000</v>
+        <v>113221900</v>
       </c>
       <c r="F54" s="3">
-        <v>116365000</v>
+        <v>116376200</v>
       </c>
       <c r="G54" s="3">
-        <v>113409000</v>
+        <v>114069800</v>
       </c>
       <c r="H54" s="3">
-        <v>110944000</v>
+        <v>111077900</v>
       </c>
       <c r="I54" s="3">
-        <v>107643000</v>
+        <v>107191400</v>
       </c>
       <c r="J54" s="3">
-        <v>103731000</v>
+        <v>103532000</v>
       </c>
       <c r="K54" s="3">
         <v>97887900</v>
@@ -2664,25 +2664,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>675100</v>
+        <v>87282100</v>
       </c>
       <c r="E57" s="3">
-        <v>532800</v>
+        <v>90574000</v>
       </c>
       <c r="F57" s="3">
-        <v>242900</v>
+        <v>93565400</v>
       </c>
       <c r="G57" s="3">
-        <v>237500</v>
+        <v>87858700</v>
       </c>
       <c r="H57" s="3">
-        <v>459700</v>
+        <v>86723800</v>
       </c>
       <c r="I57" s="3">
-        <v>420500</v>
+        <v>84288900</v>
       </c>
       <c r="J57" s="3">
-        <v>408700</v>
+        <v>81286900</v>
       </c>
       <c r="K57" s="3">
         <v>487300</v>
@@ -2709,25 +2709,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>301000</v>
+        <v>813400</v>
       </c>
       <c r="E58" s="3">
-        <v>294400</v>
+        <v>826100</v>
       </c>
       <c r="F58" s="3">
-        <v>455700</v>
+        <v>1103400</v>
       </c>
       <c r="G58" s="3">
-        <v>544700</v>
+        <v>2226700</v>
       </c>
       <c r="H58" s="3">
-        <v>667400</v>
+        <v>1650900</v>
       </c>
       <c r="I58" s="3">
-        <v>52200</v>
+        <v>1264500</v>
       </c>
       <c r="J58" s="3">
-        <v>70300</v>
+        <v>1615800</v>
       </c>
       <c r="K58" s="3">
         <v>1737300</v>
@@ -2754,25 +2754,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>205400</v>
+        <v>3632000</v>
       </c>
       <c r="E59" s="3">
-        <v>160500</v>
+        <v>3725400</v>
       </c>
       <c r="F59" s="3">
-        <v>122800</v>
+        <v>4010000</v>
       </c>
       <c r="G59" s="3">
-        <v>80000</v>
+        <v>5780900</v>
       </c>
       <c r="H59" s="3">
-        <v>269700</v>
+        <v>3031900</v>
       </c>
       <c r="I59" s="3">
-        <v>184300</v>
+        <v>2961300</v>
       </c>
       <c r="J59" s="3">
-        <v>148700</v>
+        <v>2494300</v>
       </c>
       <c r="K59" s="3">
         <v>205200</v>
@@ -2799,25 +2799,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>92401500</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>95658400</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>98921700</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>96105200</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>91866900</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>88933400</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>85804900</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2844,25 +2844,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1964000</v>
+        <v>1960600</v>
       </c>
       <c r="E61" s="3">
-        <v>1705100</v>
+        <v>1705300</v>
       </c>
       <c r="F61" s="3">
-        <v>1239300</v>
+        <v>1239500</v>
       </c>
       <c r="G61" s="3">
-        <v>1545900</v>
+        <v>1554900</v>
       </c>
       <c r="H61" s="3">
-        <v>1195200</v>
+        <v>1196700</v>
       </c>
       <c r="I61" s="3">
-        <v>1604800</v>
+        <v>1598100</v>
       </c>
       <c r="J61" s="3">
-        <v>1650600</v>
+        <v>1647400</v>
       </c>
       <c r="K61" s="3">
         <v>1811700</v>
@@ -2889,25 +2889,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>60000</v>
+        <v>1569700</v>
       </c>
       <c r="E62" s="3">
-        <v>29000</v>
+        <v>1872800</v>
       </c>
       <c r="F62" s="3">
-        <v>71700</v>
+        <v>924100</v>
       </c>
       <c r="G62" s="3">
-        <v>59000</v>
+        <v>1594400</v>
       </c>
       <c r="H62" s="3">
-        <v>74900</v>
+        <v>3784500</v>
       </c>
       <c r="I62" s="3">
-        <v>61900</v>
+        <v>3291700</v>
       </c>
       <c r="J62" s="3">
-        <v>70700</v>
+        <v>3055400</v>
       </c>
       <c r="K62" s="3">
         <v>59100</v>
@@ -3069,25 +3069,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>96467200</v>
+        <v>96268500</v>
       </c>
       <c r="E66" s="3">
-        <v>99602400</v>
+        <v>99583100</v>
       </c>
       <c r="F66" s="3">
-        <v>101523000</v>
+        <v>101493600</v>
       </c>
       <c r="G66" s="3">
-        <v>98938000</v>
+        <v>99392800</v>
       </c>
       <c r="H66" s="3">
-        <v>96932600</v>
+        <v>97002100</v>
       </c>
       <c r="I66" s="3">
-        <v>94727500</v>
+        <v>93965600</v>
       </c>
       <c r="J66" s="3">
-        <v>91115900</v>
+        <v>90578200</v>
       </c>
       <c r="K66" s="3">
         <v>87220000</v>
@@ -3313,25 +3313,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7052000</v>
+        <v>6904800</v>
       </c>
       <c r="E72" s="3">
-        <v>6820300</v>
+        <v>6689600</v>
       </c>
       <c r="F72" s="3">
-        <v>7084100</v>
+        <v>6966900</v>
       </c>
       <c r="G72" s="3">
-        <v>6753500</v>
+        <v>6650600</v>
       </c>
       <c r="H72" s="3">
-        <v>6588100</v>
+        <v>6423200</v>
       </c>
       <c r="I72" s="3">
-        <v>6526400</v>
+        <v>6360400</v>
       </c>
       <c r="J72" s="3">
-        <v>6186600</v>
+        <v>6122900</v>
       </c>
       <c r="K72" s="3">
         <v>5385800</v>
@@ -3493,25 +3493,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13856900</v>
+        <v>13833200</v>
       </c>
       <c r="E76" s="3">
-        <v>13602300</v>
+        <v>13604300</v>
       </c>
       <c r="F76" s="3">
-        <v>14842100</v>
+        <v>14843600</v>
       </c>
       <c r="G76" s="3">
-        <v>14471100</v>
+        <v>14555400</v>
       </c>
       <c r="H76" s="3">
-        <v>14011700</v>
+        <v>14028600</v>
       </c>
       <c r="I76" s="3">
-        <v>12915300</v>
+        <v>12861200</v>
       </c>
       <c r="J76" s="3">
-        <v>12614800</v>
+        <v>12590600</v>
       </c>
       <c r="K76" s="3">
         <v>10667900</v>
@@ -3633,25 +3633,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>451600</v>
+        <v>527100</v>
       </c>
       <c r="E81" s="3">
-        <v>468200</v>
+        <v>559000</v>
       </c>
       <c r="F81" s="3">
-        <v>571800</v>
+        <v>675800</v>
       </c>
       <c r="G81" s="3">
-        <v>361900</v>
+        <v>466100</v>
       </c>
       <c r="H81" s="3">
-        <v>330800</v>
+        <v>418500</v>
       </c>
       <c r="I81" s="3">
-        <v>743200</v>
+        <v>831100</v>
       </c>
       <c r="J81" s="3">
-        <v>1121600</v>
+        <v>1196300</v>
       </c>
       <c r="K81" s="3">
         <v>412700</v>
@@ -3697,25 +3697,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>105100</v>
+        <v>103300</v>
       </c>
       <c r="E83" s="3">
-        <v>112200</v>
+        <v>110600</v>
       </c>
       <c r="F83" s="3">
-        <v>124300</v>
+        <v>122500</v>
       </c>
       <c r="G83" s="3">
-        <v>127600</v>
+        <v>126500</v>
       </c>
       <c r="H83" s="3">
-        <v>120700</v>
+        <v>119000</v>
       </c>
       <c r="I83" s="3">
-        <v>62400</v>
+        <v>60400</v>
       </c>
       <c r="J83" s="3">
-        <v>63900</v>
+        <v>59600</v>
       </c>
       <c r="K83" s="3">
         <v>68000</v>
@@ -3967,25 +3967,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-2169400</v>
+        <v>959100</v>
       </c>
       <c r="E89" s="3">
-        <v>140300</v>
+        <v>3127900</v>
       </c>
       <c r="F89" s="3">
-        <v>1240800</v>
+        <v>-4964400</v>
       </c>
       <c r="G89" s="3">
-        <v>2265100</v>
+        <v>1547300</v>
       </c>
       <c r="H89" s="3">
-        <v>1145600</v>
+        <v>-831000</v>
       </c>
       <c r="I89" s="3">
-        <v>337900</v>
+        <v>-2849700</v>
       </c>
       <c r="J89" s="3">
-        <v>1624000</v>
+        <v>-3037800</v>
       </c>
       <c r="K89" s="3">
         <v>-2396100</v>
@@ -4031,7 +4031,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-87200</v>
+        <v>-87000</v>
       </c>
       <c r="E91" s="3">
         <v>-71200</v>
@@ -4040,16 +4040,16 @@
         <v>-77600</v>
       </c>
       <c r="G91" s="3">
-        <v>-76800</v>
+        <v>-77300</v>
       </c>
       <c r="H91" s="3">
-        <v>-129500</v>
+        <v>-129700</v>
       </c>
       <c r="I91" s="3">
-        <v>-84200</v>
+        <v>-83900</v>
       </c>
       <c r="J91" s="3">
-        <v>-52400</v>
+        <v>-52300</v>
       </c>
       <c r="K91" s="3">
         <v>-57300</v>
@@ -4166,25 +4166,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-65500</v>
+        <v>-65400</v>
       </c>
       <c r="E94" s="3">
-        <v>273600</v>
+        <v>273700</v>
       </c>
       <c r="F94" s="3">
-        <v>342600</v>
+        <v>342700</v>
       </c>
       <c r="G94" s="3">
-        <v>47200</v>
+        <v>47500</v>
       </c>
       <c r="H94" s="3">
-        <v>-14700</v>
+        <v>-14800</v>
       </c>
       <c r="I94" s="3">
-        <v>-81200</v>
+        <v>-80800</v>
       </c>
       <c r="J94" s="3">
-        <v>535400</v>
+        <v>534300</v>
       </c>
       <c r="K94" s="3">
         <v>231000</v>
@@ -4230,25 +4230,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-176600</v>
+        <v>252600</v>
       </c>
       <c r="E96" s="3">
-        <v>-331300</v>
+        <v>256200</v>
       </c>
       <c r="F96" s="3">
-        <v>-216200</v>
+        <v>320200</v>
       </c>
       <c r="G96" s="3">
-        <v>-174100</v>
+        <v>277300</v>
       </c>
       <c r="H96" s="3">
-        <v>-105500</v>
+        <v>170000</v>
       </c>
       <c r="I96" s="3">
-        <v>-106700</v>
+        <v>170200</v>
       </c>
       <c r="J96" s="3">
-        <v>-270100</v>
+        <v>319300</v>
       </c>
       <c r="K96" s="3">
         <v>-59800</v>
@@ -4410,25 +4410,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-223400</v>
+        <v>-3347700</v>
       </c>
       <c r="E100" s="3">
-        <v>-1023900</v>
+        <v>-4011600</v>
       </c>
       <c r="F100" s="3">
-        <v>-847700</v>
+        <v>5357500</v>
       </c>
       <c r="G100" s="3">
-        <v>-205800</v>
+        <v>523900</v>
       </c>
       <c r="H100" s="3">
-        <v>51800</v>
+        <v>2029900</v>
       </c>
       <c r="I100" s="3">
-        <v>-327800</v>
+        <v>2859800</v>
       </c>
       <c r="J100" s="3">
-        <v>-1062800</v>
+        <v>3598000</v>
       </c>
       <c r="K100" s="3">
         <v>-1689500</v>
@@ -4455,25 +4455,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-108200</v>
+        <v>-108000</v>
       </c>
       <c r="E101" s="3">
-        <v>-479600</v>
+        <v>-479700</v>
       </c>
       <c r="F101" s="3">
         <v>154800</v>
       </c>
       <c r="G101" s="3">
-        <v>338100</v>
+        <v>340100</v>
       </c>
       <c r="H101" s="3">
-        <v>-77600</v>
+        <v>-77700</v>
       </c>
       <c r="I101" s="3">
-        <v>-436800</v>
+        <v>-434900</v>
       </c>
       <c r="J101" s="3">
-        <v>716400</v>
+        <v>715000</v>
       </c>
       <c r="K101" s="3">
         <v>-635700</v>
@@ -4500,25 +4500,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2566500</v>
+        <v>-2562100</v>
       </c>
       <c r="E102" s="3">
-        <v>-1089600</v>
+        <v>-1089700</v>
       </c>
       <c r="F102" s="3">
-        <v>890400</v>
+        <v>890500</v>
       </c>
       <c r="G102" s="3">
-        <v>2444600</v>
+        <v>2458800</v>
       </c>
       <c r="H102" s="3">
-        <v>1105100</v>
+        <v>1106400</v>
       </c>
       <c r="I102" s="3">
-        <v>-507800</v>
+        <v>-505700</v>
       </c>
       <c r="J102" s="3">
-        <v>1813000</v>
+        <v>1809600</v>
       </c>
       <c r="K102" s="3">
         <v>-4490400</v>

--- a/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>BKEAY</t>
   </si>
@@ -656,120 +656,126 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1986000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1861400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1729300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2029200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1587700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1604800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1991600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1975400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2603200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3004200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3243000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3229100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2915200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2671100</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -812,36 +818,39 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1986000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1861400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1729300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2029200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1587700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1604800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1991600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1975400</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -857,9 +866,12 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -877,8 +889,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -921,9 +934,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,36 +982,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E14" s="3">
         <v>11000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>21700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>16300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-58700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>24400</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1011,54 +1030,60 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>78400</v>
+      </c>
+      <c r="E15" s="3">
         <v>71700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>74400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>76300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>73500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>69800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>62200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>63700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-63900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-67100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-88700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-90400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-88900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-85600</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1073,98 +1098,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1238900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1206500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1181900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1194200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1154200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1268100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1091600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1027800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1627000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1743200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1754400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1721800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1690200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1495000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>747100</v>
+      </c>
+      <c r="E18" s="3">
         <v>654900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>547400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>835000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>433500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>336800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>900000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>947600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>976200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1261000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1488600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1507300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1224900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1176100</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1182,98 +1214,105 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-35800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-108000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>31800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-38200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-78100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-70500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-45100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-389100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-447600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-415400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-414900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-250600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-439900</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>848900</v>
+      </c>
+      <c r="E21" s="3">
         <v>762400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>729700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>879500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>545200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>484700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1032600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1056400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>655000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>1063200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>821800</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1298,8 +1337,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1316,99 +1355,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>751900</v>
+      </c>
+      <c r="E23" s="3">
         <v>679700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>633700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>786900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>465100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>410600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1029200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>968200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>587000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>813400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1073100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1092400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>974300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>736100</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>155900</v>
+      </c>
+      <c r="E24" s="3">
         <v>150300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>72200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>105500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-10200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-17700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>192300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>152900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>136400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>133600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>210200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>229000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>181700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>166400</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1451,99 +1499,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>595900</v>
+      </c>
+      <c r="E26" s="3">
         <v>529500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>561500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>681400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>475300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>428300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>836900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>815300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>450600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>679800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>862900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>863400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>792600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>569700</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>516800</v>
+      </c>
+      <c r="E27" s="3">
         <v>450900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>468200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>571800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>364000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>331200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>740100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1119500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>373800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>597400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>806500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>808800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>737300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>515800</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1586,9 +1643,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1611,17 +1671,17 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>530500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>38900</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>38500</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N29" s="3" t="s">
         <v>5</v>
       </c>
@@ -1631,9 +1691,12 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1676,9 +1739,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1721,99 +1787,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E32" s="3">
         <v>35800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>108000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-31800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>38200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>78100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>70500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>45100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>389100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>447600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>415400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>414900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>250600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>439900</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>593200</v>
+      </c>
+      <c r="E33" s="3">
         <v>527100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>559000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>675800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>466100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>418500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>831100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1196300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>412700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>635900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>806500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>808800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>737300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>515800</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1856,104 +1931,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>593200</v>
+      </c>
+      <c r="E35" s="3">
         <v>527100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>559000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>675800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>466100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>418500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>831100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1196300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>412700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>635900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>806500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>808800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>737300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>515800</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1971,8 +2055,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1990,98 +2075,105 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5317500</v>
+      </c>
+      <c r="E41" s="3">
         <v>11709800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13398600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15471200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14662100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12148900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10771400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10856800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8390700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8810000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8969800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8854000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11013100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9185400</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5752600</v>
+      </c>
+      <c r="E42" s="3">
         <v>2154500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1707900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1056700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1722900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3524900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2577700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2797900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9317900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>14808500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>16124900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>17747500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>14642900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>14219400</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2106,8 +2198,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2124,36 +2216,39 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>177400</v>
+      </c>
+      <c r="E44" s="3">
         <v>218100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>53400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>25000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>30800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>28900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>18800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>190100</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -2169,36 +2264,39 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4736700</v>
+      </c>
+      <c r="E45" s="3">
         <v>3929200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3993800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4290400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5970700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3131400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3270200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2730800</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2214,36 +2312,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15984200</v>
+      </c>
+      <c r="E46" s="3">
         <v>19149600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20490400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22366800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24111100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20778600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19183200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>20197400</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2259,144 +2360,156 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>25579300</v>
+      </c>
+      <c r="E47" s="3">
         <v>20501800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>19911900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>19414400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>18755700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>20159400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>19352800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>18101500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>768400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>734200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>774900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>615200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>602400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>489000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1028900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1073800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1065800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1135200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1174200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1154800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1010800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>978200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1532800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1694000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1671000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1741700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1616600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1617800</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>236400</v>
+      </c>
+      <c r="E49" s="3">
         <v>237100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>239800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>241700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>246600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>247300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>247700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>250700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>337400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>494700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>503800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>513600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>520400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>539500</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2439,9 +2552,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2484,54 +2600,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1828400</v>
+      </c>
+      <c r="E52" s="3">
         <v>1430800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1647200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1778100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2342100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2108800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1838300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1951000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>741100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>23100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>48300</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2574,54 +2696,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>113004100</v>
+      </c>
+      <c r="E54" s="3">
         <v>110135400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>113221900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>116376200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>114069800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>111077900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>107191400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>103532000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>97887900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>99545800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>101389000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>97056500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>89137400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>78259500</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2639,8 +2767,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2658,170 +2787,180 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>88680800</v>
+      </c>
+      <c r="E57" s="3">
         <v>87282100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>90574000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>93565400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>87858700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>86723800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>84288900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>81286900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>487300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>543900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>618200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>531800</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>746200</v>
+      </c>
+      <c r="E58" s="3">
         <v>813400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>826100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1103400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2226700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1650900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1264500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1615800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1737300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>989100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1747800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>443900</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>437600</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>240700</v>
+      </c>
+      <c r="E59" s="3">
         <v>3632000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3725400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4010000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5780900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3031900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2961300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2494300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>205200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>168800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>149300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>174200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>127200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>60500</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>89667700</v>
+      </c>
+      <c r="E60" s="3">
         <v>92401500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>95658400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>98921700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>96105200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>91866900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>88933400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>85804900</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2837,99 +2976,108 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3022300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1960600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1705300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1239500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1554900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1196700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1598100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1647400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1811700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2908400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3317100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1919600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2951900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2554400</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6612800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1569700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1872800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>924100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1594400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3784500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3291700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3055400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>59100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>68000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>87400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>83300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>80600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>59000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2972,9 +3120,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3017,9 +3168,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3062,54 +3216,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>99391100</v>
+      </c>
+      <c r="E66" s="3">
         <v>96268500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>99583100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>101493600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>99392800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>97002100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>93965600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>90578200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>87220000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>89044300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>92613900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>88858700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>81776600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>72164600</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3127,8 +3287,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3171,9 +3332,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3216,9 +3380,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3261,9 +3428,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3306,54 +3476,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6591400</v>
+      </c>
+      <c r="E72" s="3">
         <v>6904800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6689600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6966900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6650600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6423200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6360400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6122900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5385800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5190000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4890600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6753700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6013600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4971100</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3396,9 +3572,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3441,9 +3620,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3486,54 +3668,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13577600</v>
+      </c>
+      <c r="E76" s="3">
         <v>13833200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13604300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14843600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14555400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14028600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12861200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12590600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10667900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10501500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8774600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8197800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7360700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6094800</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3576,104 +3764,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>593200</v>
+      </c>
+      <c r="E81" s="3">
         <v>527100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>559000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>675800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>466100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>418500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>831100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1196300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>412700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>635900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>806500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>808800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>737300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>515800</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3691,53 +3888,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E83" s="3">
         <v>103300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>110600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>122500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>126500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>119000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>60400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>59600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>68000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>88900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>85600</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3780,9 +3981,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3825,9 +4029,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3870,9 +4077,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3915,9 +4125,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3960,54 +4173,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-997000</v>
+      </c>
+      <c r="E89" s="3">
         <v>959100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3127900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4964400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1547300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-831000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2849700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3037800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2396100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4688100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2322300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2346700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>532200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1907700</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4025,53 +4244,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-69100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-87000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-71200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-77600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-77300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-129700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-83900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-52300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-57300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-38900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-95500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-96500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-56200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-73900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4114,9 +4337,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4159,54 +4385,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-65400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>273700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>342700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>47500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-80800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>534300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>231000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>84400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>72300</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4224,53 +4456,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>225300</v>
+      </c>
+      <c r="E96" s="3">
         <v>252600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>256200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>320200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>277300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>170000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>170200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>319300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-59800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-126300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-95200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-96200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-120000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-148100</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4313,9 +4549,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4358,9 +4597,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4403,84 +4645,90 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>636500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3347700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4011600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5357500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>523900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2029900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2859800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3598000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1689500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>2031000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1043700</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-147500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-108000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-479700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>154800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>340100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-77700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-434900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>715000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-635700</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
@@ -4493,52 +4741,58 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-549000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2562100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1089700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>890500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2458800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1106400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-505700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1809600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4490400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2295900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1239600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1252700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2647500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-791700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
@@ -1105,10 +1105,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1238900</v>
+        <v>1240600</v>
       </c>
       <c r="E17" s="3">
-        <v>1206500</v>
+        <v>1208200</v>
       </c>
       <c r="F17" s="3">
         <v>1181900</v>
@@ -1153,10 +1153,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>747100</v>
+        <v>745400</v>
       </c>
       <c r="E18" s="3">
-        <v>654900</v>
+        <v>653200</v>
       </c>
       <c r="F18" s="3">
         <v>547400</v>
@@ -1221,10 +1221,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-23400</v>
+        <v>-25100</v>
       </c>
       <c r="E20" s="3">
-        <v>-35800</v>
+        <v>-37500</v>
       </c>
       <c r="F20" s="3">
         <v>-108000</v>
@@ -1797,10 +1797,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>23400</v>
+        <v>25100</v>
       </c>
       <c r="E32" s="3">
-        <v>35800</v>
+        <v>37500</v>
       </c>
       <c r="F32" s="3">
         <v>108000</v>
@@ -2082,10 +2082,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5317500</v>
+        <v>11312500</v>
       </c>
       <c r="E41" s="3">
-        <v>11709800</v>
+        <v>11794000</v>
       </c>
       <c r="F41" s="3">
         <v>13398600</v>
@@ -2130,7 +2130,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>5752600</v>
+        <v>1103800</v>
       </c>
       <c r="E42" s="3">
         <v>2154500</v>
@@ -2322,10 +2322,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>15984200</v>
+        <v>18358400</v>
       </c>
       <c r="E46" s="3">
-        <v>19149600</v>
+        <v>19233900</v>
       </c>
       <c r="F46" s="3">
         <v>20490400</v>
@@ -2370,10 +2370,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>25579300</v>
+        <v>23205000</v>
       </c>
       <c r="E47" s="3">
-        <v>20501800</v>
+        <v>20417600</v>
       </c>
       <c r="F47" s="3">
         <v>19911900</v>
@@ -2842,7 +2842,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>746200</v>
+        <v>1425200</v>
       </c>
       <c r="E58" s="3">
         <v>813400</v>
@@ -2890,7 +2890,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>240700</v>
+        <v>4465700</v>
       </c>
       <c r="E59" s="3">
         <v>3632000</v>
@@ -2938,7 +2938,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>89667700</v>
+        <v>95172400</v>
       </c>
       <c r="E60" s="3">
         <v>92401500</v>
@@ -2986,7 +2986,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3022300</v>
+        <v>2441800</v>
       </c>
       <c r="E61" s="3">
         <v>1960600</v>
@@ -3034,7 +3034,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6612800</v>
+        <v>1436800</v>
       </c>
       <c r="E62" s="3">
         <v>1569700</v>
@@ -3486,7 +3486,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>6591400</v>
+        <v>7255500</v>
       </c>
       <c r="E72" s="3">
         <v>6904800</v>

--- a/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
@@ -2890,7 +2890,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4465700</v>
+        <v>4474200</v>
       </c>
       <c r="E59" s="3">
         <v>3632000</v>
@@ -2938,7 +2938,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>95172400</v>
+        <v>95180900</v>
       </c>
       <c r="E60" s="3">
         <v>92401500</v>
@@ -3034,7 +3034,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1436800</v>
+        <v>1428300</v>
       </c>
       <c r="E62" s="3">
         <v>1569700</v>

--- a/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BKEAY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>BKEAY</t>
   </si>
@@ -656,126 +656,132 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1975500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1986000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1861400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1729300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2029200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1587700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1604800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1991600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1975400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2603200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3004200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3243000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3229100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2915200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2671100</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -821,39 +827,42 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1975500</v>
+      </c>
+      <c r="E10" s="3">
         <v>1986000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1861400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1729300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2029200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1587700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1604800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1991600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1975400</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -869,9 +878,12 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,8 +902,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -937,9 +950,12 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,39 +1001,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>92900</v>
+      </c>
+      <c r="E14" s="3">
         <v>18700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>11000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>21700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>16300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-58700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>24400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1033,57 +1052,63 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E15" s="3">
         <v>78400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>71700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>74400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>76300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>73500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>69800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>62200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>63700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-63900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-67100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-88700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-90400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-88900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-85600</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1099,104 +1124,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1261800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1240600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1208200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1181900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1194200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1154200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1268100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1091600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1027800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1627000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1743200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1754400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1721800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1690200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1495000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>713700</v>
+      </c>
+      <c r="E18" s="3">
         <v>745400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>653200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>547400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>835000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>433500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>336800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>900000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>947600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>976200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1261000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1488600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1507300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1224900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1176100</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1215,104 +1247,111 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-25100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-37500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-108000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>31800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-38200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-78100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-70500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-45100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-389100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-447600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-415400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-414900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-250600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-439900</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>721300</v>
+      </c>
+      <c r="E21" s="3">
         <v>848900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>762400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>729700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>879500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>545200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>484700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1032600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1056400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>655000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>1063200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>821800</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1379,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1358,105 +1397,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>581600</v>
+      </c>
+      <c r="E23" s="3">
         <v>751900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>679700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>633700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>786900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>465100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>410600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1029200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>968200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>587000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>813400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1073100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1092400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>974300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>736100</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>127800</v>
+      </c>
+      <c r="E24" s="3">
         <v>155900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>150300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>72200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>105500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-10200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-17700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>192300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>152900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>136400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>133600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>210200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>229000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>181700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>166400</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1502,105 +1550,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>453800</v>
+      </c>
+      <c r="E26" s="3">
         <v>595900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>529500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>561500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>681400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>475300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>428300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>836900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>815300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>450600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>679800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>862900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>863400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>792600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>569700</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>412000</v>
+      </c>
+      <c r="E27" s="3">
         <v>516800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>450900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>468200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>571800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>364000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>331200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>740100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1119500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>373800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>597400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>806500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>808800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>737300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>515800</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1646,9 +1703,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,17 +1734,17 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>530500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>38900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>38500</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O29" s="3" t="s">
         <v>5</v>
       </c>
@@ -1694,9 +1754,12 @@
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1742,9 +1805,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1790,105 +1856,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-39200</v>
+      </c>
+      <c r="E32" s="3">
         <v>25100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>37500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>108000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-31800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>38200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>78100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>70500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>45100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>389100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>447600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>415400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>414900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>250600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>439900</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>449800</v>
+      </c>
+      <c r="E33" s="3">
         <v>593200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>527100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>559000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>675800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>466100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>418500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>831100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1196300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>412700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>635900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>806500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>808800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>737300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>515800</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1934,110 +2009,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>449800</v>
+      </c>
+      <c r="E35" s="3">
         <v>593200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>527100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>559000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>675800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>466100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>418500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>831100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1196300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>412700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>635900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>806500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>808800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>737300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>515800</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2056,8 +2140,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2076,104 +2161,111 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11903100</v>
+      </c>
+      <c r="E41" s="3">
         <v>11312500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11794000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13398600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15471200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14662100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12148900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10771400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10856800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8390700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8810000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8969800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8854000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11013100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9185400</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>803500</v>
+      </c>
+      <c r="E42" s="3">
         <v>1103800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2154500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1707900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1056700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1722900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3524900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2577700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2797900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9317900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>14808500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>16124900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>17747500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>14642900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>14219400</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2201,8 +2293,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2219,39 +2311,42 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E44" s="3">
         <v>177400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>218100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>53400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>25000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>30800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>28900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>18800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>190100</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -2267,39 +2362,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4927300</v>
+      </c>
+      <c r="E45" s="3">
         <v>4736700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3929200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3993800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4290400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5970700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3131400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3270200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2730800</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2315,39 +2413,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18771000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18358400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19233900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20490400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22366800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24111100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20778600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19183200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>20197400</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2363,153 +2464,165 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>25615300</v>
+      </c>
+      <c r="E47" s="3">
         <v>23205000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>20417600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>19911900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>19414400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>18755700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20159400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>19352800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>18101500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>768400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>734200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>774900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>615200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>602400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>489000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>820700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1028900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1073800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1065800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1135200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1174200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1154800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1010800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>978200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1532800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1694000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1671000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1741700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1616600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1617800</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>392100</v>
+      </c>
+      <c r="E49" s="3">
         <v>236400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>237100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>239800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>241700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>246600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>247300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>247700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>250700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>337400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>494700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>503800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>513600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>520400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>539500</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2555,9 +2668,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2603,57 +2719,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2234400</v>
+      </c>
+      <c r="E52" s="3">
         <v>1828400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1430800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1647200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1778100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2342100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2108800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1838300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1951000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>741100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>48300</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2699,57 +2821,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>118327200</v>
+      </c>
+      <c r="E54" s="3">
         <v>113004100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>110135400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>113221900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>116376200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>114069800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>111077900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>107191400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>103532000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>97887900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>99545800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>101389000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>97056500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>89137400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>78259500</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2768,8 +2896,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2788,182 +2917,192 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>94934900</v>
+      </c>
+      <c r="E57" s="3">
         <v>88680800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>87282100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>90574000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>93565400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>87858700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>86723800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>84288900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>81286900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>487300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>543900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>618200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>531800</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1396400</v>
+      </c>
+      <c r="E58" s="3">
         <v>1425200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>813400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>826100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1103400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2226700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1650900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1264500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1615800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1737300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>989100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1747800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>443900</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>437600</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4724400</v>
+      </c>
+      <c r="E59" s="3">
         <v>4474200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3632000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3725400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4010000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5780900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3031900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2961300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2494300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>205200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>168800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>149300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>174200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>127200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>60500</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>101674700</v>
+      </c>
+      <c r="E60" s="3">
         <v>95180900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>92401500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>95658400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>98921700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>96105200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>91866900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>88933400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>85804900</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2979,105 +3118,114 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1643100</v>
+      </c>
+      <c r="E61" s="3">
         <v>2441800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1960600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1705300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1239500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1554900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1196700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1598100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1647400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1811700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2908400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3317100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1919600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2951900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2554400</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1098000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1428300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1569700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1872800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>924100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1594400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3784500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3291700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3055400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>59100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>68000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>87400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>83300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>80600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>59000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3123,9 +3271,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3171,9 +3322,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3219,57 +3373,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>104756000</v>
+      </c>
+      <c r="E66" s="3">
         <v>99391100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>96268500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>99583100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>101493600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>99392800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>97002100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>93965600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>90578200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>87220000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>89044300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>92613900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>88858700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>81776600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>72164600</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3288,8 +3448,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3335,9 +3496,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3383,9 +3547,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3431,9 +3598,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3479,57 +3649,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7392600</v>
+      </c>
+      <c r="E72" s="3">
         <v>7255500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6904800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6689600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6966900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6650600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6423200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6360400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6122900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5385800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5190000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4890600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6753700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6013600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4971100</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3575,9 +3751,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3623,9 +3802,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3671,57 +3853,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13533200</v>
+      </c>
+      <c r="E76" s="3">
         <v>13577600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13833200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13604300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14843600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14555400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14028600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12861200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12590600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10667900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10501500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8774600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8197800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7360700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6094800</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3767,110 +3955,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>449800</v>
+      </c>
+      <c r="E81" s="3">
         <v>593200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>527100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>559000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>675800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>466100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>418500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>831100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1196300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>412700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>635900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>806500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>808800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>737300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>515800</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3889,56 +4086,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E83" s="3">
         <v>111000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>103300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>110600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>122500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>126500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>119000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>60400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>59600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>68000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>88900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>85600</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3984,9 +4185,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4032,9 +4236,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4080,9 +4287,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4128,9 +4338,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4176,57 +4389,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4251600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-997000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>959100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3127900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4964400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1547300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-831000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2849700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3037800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2396100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4688100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2322300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2346700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>532200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1907700</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4245,56 +4464,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-52300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-69100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-87000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-71200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-77600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-77300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-129700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-83900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-52300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-57300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-38900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-95500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-96500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-56200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-73900</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4340,9 +4563,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4388,57 +4614,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-149200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-40900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-65400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>273700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>342700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>47500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-80800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>534300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>231000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>84400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>72300</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4457,56 +4689,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>282800</v>
+      </c>
+      <c r="E96" s="3">
         <v>225300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>252600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>256200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>320200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>277300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>170000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>170200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>319300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-59800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-126300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-95200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-96200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-120000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-148100</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4552,9 +4788,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4600,9 +4839,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4648,90 +4890,96 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4813300</v>
+      </c>
+      <c r="E100" s="3">
         <v>636500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3347700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4011600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5357500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>523900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2029900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2859800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3598000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1689500</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>2031000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1043700</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>201300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-147500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-108000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-479700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>154800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>340100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-77700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-434900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>715000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-635700</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
@@ -4744,55 +4992,61 @@
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>613900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-549000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2562100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1089700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>890500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2458800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1106400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-505700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1809600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4490400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2295900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1239600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1252700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2647500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-791700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
